--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,6 +38,21 @@
     <x:t>ACSEL</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
@@ -47,15 +62,99 @@
     <x:t>BAKAB</x:t>
   </x:si>
   <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
     <x:t>BVSAN</x:t>
   </x:si>
   <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARFA</x:t>
   </x:si>
   <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONCSM</x:t>
   </x:si>
   <x:si>
@@ -65,91 +164,106 @@
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
     <x:t>RTALB</x:t>
   </x:si>
   <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>TATEN</x:t>
   </x:si>
   <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>YEOTK</x:t>
   </x:si>
   <x:si>
     <x:t>YUNSA</x:t>
   </x:si>
   <x:si>
+    <x:t>ZEDUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>AEFES</x:t>
   </x:si>
   <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKFGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
+    <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
     <x:t>ALGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANSGR</x:t>
   </x:si>
   <x:si>
     <x:t>ARASE</x:t>
   </x:si>
   <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>AVPGY</x:t>
   </x:si>
   <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
     <x:t>BRISA</x:t>
   </x:si>
   <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
+    <x:t>CELHA</x:t>
   </x:si>
   <x:si>
     <x:t>CWENE</x:t>
@@ -158,31 +272,19 @@
     <x:t>DCTTR</x:t>
   </x:si>
   <x:si>
-    <x:t>DIRIT</x:t>
+    <x:t>DGATE</x:t>
   </x:si>
   <x:si>
     <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
     <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
     <x:t>ECZYT</x:t>
   </x:si>
   <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
+    <x:t>ETILR</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
@@ -194,19 +296,19 @@
     <x:t>GEREL</x:t>
   </x:si>
   <x:si>
-    <x:t>GESAN</x:t>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
   </x:si>
   <x:si>
     <x:t>GUBRF</x:t>
   </x:si>
   <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
     <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>HURGZ</x:t>
+    <x:t>HUBVC</x:t>
   </x:si>
   <x:si>
     <x:t>ICBCT</x:t>
@@ -215,34 +317,7 @@
     <x:t>IHAAS</x:t>
   </x:si>
   <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
+    <x:t>KAYSE</x:t>
   </x:si>
   <x:si>
     <x:t>KTLEV</x:t>
@@ -251,52 +326,31 @@
     <x:t>KTSKR</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
     <x:t>MAGEN</x:t>
   </x:si>
   <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPARK</x:t>
   </x:si>
   <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
+    <x:t>NTGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
-    <x:t>OZATD</x:t>
+    <x:t>OZGYO</x:t>
   </x:si>
   <x:si>
     <x:t>OZSUB</x:t>
@@ -308,55 +362,28 @@
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETKM</x:t>
   </x:si>
   <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>PSGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
   </x:si>
   <x:si>
     <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
+    <x:t>TOASO</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
@@ -365,19 +392,13 @@
     <x:t>TURSG</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
+    <x:t>VANGD</x:t>
   </x:si>
   <x:si>
     <x:t>VKGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -728,7 +749,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C18"/>
+  <x:dimension ref="A1:C64"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -926,6 +947,512 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:3">
+      <x:c r="A64" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -943,7 +1470,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C100"/>
+  <x:dimension ref="A1:C61"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -959,7 +1486,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -970,7 +1497,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -981,7 +1508,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -992,7 +1519,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1003,7 +1530,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1014,7 +1541,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1025,7 +1552,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1036,7 +1563,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1047,7 +1574,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1058,7 +1585,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1069,7 +1596,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1080,7 +1607,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1091,7 +1618,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1102,7 +1629,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1113,7 +1640,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1124,7 +1651,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1135,7 +1662,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1146,7 +1673,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1157,7 +1684,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1168,7 +1695,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1179,7 +1706,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1190,7 +1717,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1201,7 +1728,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1212,7 +1739,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1223,7 +1750,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1234,7 +1761,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1245,7 +1772,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1256,7 +1783,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1267,7 +1794,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1278,7 +1805,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1289,7 +1816,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1300,7 +1827,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1311,7 +1838,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1322,7 +1849,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1333,7 +1860,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1344,7 +1871,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1355,7 +1882,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1366,7 +1893,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1377,7 +1904,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1388,7 +1915,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1399,7 +1926,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1410,7 +1937,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1421,7 +1948,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1432,7 +1959,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1443,7 +1970,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1454,7 +1981,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1465,7 +1992,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -1476,7 +2003,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -1487,7 +2014,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -1498,7 +2025,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -1509,7 +2036,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -1520,7 +2047,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -1531,7 +2058,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -1542,7 +2069,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -1553,7 +2080,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -1564,7 +2091,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -1575,7 +2102,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -1586,7 +2113,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -1597,7 +2124,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -1608,441 +2135,12 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:3">
-      <x:c r="A63" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:3">
-      <x:c r="A64" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:3">
-      <x:c r="A65" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:3">
-      <x:c r="A66" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:3">
-      <x:c r="A67" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:3">
-      <x:c r="A68" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:3">
-      <x:c r="A69" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:3">
-      <x:c r="A70" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:3">
-      <x:c r="A71" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:3">
-      <x:c r="A72" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:3">
-      <x:c r="A73" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:3">
-      <x:c r="A74" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:3">
-      <x:c r="A75" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:3">
-      <x:c r="A76" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:3">
-      <x:c r="A77" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:3">
-      <x:c r="A78" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:3">
-      <x:c r="A79" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:3">
-      <x:c r="A80" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:3">
-      <x:c r="A81" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:3">
-      <x:c r="A82" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:3">
-      <x:c r="A83" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:3">
-      <x:c r="A84" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:3">
-      <x:c r="A85" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:3">
-      <x:c r="A86" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:3">
-      <x:c r="A87" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:3">
-      <x:c r="A88" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:3">
-      <x:c r="A89" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:3">
-      <x:c r="A90" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:3">
-      <x:c r="A91" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:3">
-      <x:c r="A92" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:3">
-      <x:c r="A93" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:3">
-      <x:c r="A94" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:3">
-      <x:c r="A95" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:3">
-      <x:c r="A96" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:3">
-      <x:c r="A97" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:3">
-      <x:c r="A98" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:3">
-      <x:c r="A99" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:3">
-      <x:c r="A100" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>A1YEN</x:t>
+    <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,370 +35,247 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
   </x:si>
   <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
   </x:si>
   <x:si>
     <x:t>BESLR</x:t>
   </x:si>
   <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
     <x:t>DOGUB</x:t>
   </x:si>
   <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
+    <x:t>ISKPL</x:t>
   </x:si>
   <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
     <x:t>KRVGD</x:t>
   </x:si>
   <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVVA</x:t>
   </x:si>
   <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>SEGMN</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>TATGD</x:t>
   </x:si>
   <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZEDUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -749,7 +626,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C64"/>
+  <x:dimension ref="A1:C37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1156,303 +1033,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:3">
-      <x:c r="A63" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:3">
-      <x:c r="A64" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1470,7 +1050,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C61"/>
+  <x:dimension ref="A1:C47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1486,7 +1066,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1497,7 +1077,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1508,7 +1088,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1519,7 +1099,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1530,7 +1110,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1541,7 +1121,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1552,7 +1132,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1563,7 +1143,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1574,7 +1154,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1585,7 +1165,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1596,7 +1176,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1607,7 +1187,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1618,7 +1198,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1629,7 +1209,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1640,7 +1220,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1651,7 +1231,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1662,7 +1242,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1673,7 +1253,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1684,7 +1264,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1695,7 +1275,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1706,7 +1286,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1717,7 +1297,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1728,7 +1308,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1739,7 +1319,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1750,7 +1330,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1761,7 +1341,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1772,7 +1352,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1783,7 +1363,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1794,7 +1374,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1805,7 +1385,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1816,7 +1396,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1827,7 +1407,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1838,7 +1418,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1849,7 +1429,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1860,7 +1440,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1871,7 +1451,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1882,7 +1462,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1893,7 +1473,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1904,7 +1484,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1915,7 +1495,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1926,7 +1506,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1937,7 +1517,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1948,7 +1528,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1959,7 +1539,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1970,7 +1550,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1981,166 +1561,12 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,49 +26,151 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
   </x:si>
   <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
   </x:si>
   <x:si>
     <x:t>CVKMD</x:t>
   </x:si>
   <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
@@ -77,205 +179,52 @@
     <x:t>FONET</x:t>
   </x:si>
   <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>ONCSM</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
+    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>VERUS</x:t>
+    <x:t>TEZOL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -626,7 +575,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C37"/>
+  <x:dimension ref="A1:C38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1033,6 +982,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1050,7 +1010,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C47"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1066,7 +1026,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1077,7 +1037,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1088,7 +1048,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1099,7 +1059,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1110,7 +1070,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1121,7 +1081,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1132,7 +1092,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1143,7 +1103,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1154,7 +1114,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1165,7 +1125,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1176,7 +1136,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1187,7 +1147,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1198,7 +1158,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1209,7 +1169,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1220,7 +1180,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1231,7 +1191,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1242,7 +1202,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1253,7 +1213,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1264,7 +1224,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1275,7 +1235,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1286,7 +1246,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1297,7 +1257,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1308,7 +1268,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1319,7 +1279,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1330,7 +1290,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1341,7 +1301,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1352,7 +1312,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1363,210 +1323,12 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>DCTTR</x:t>
+    <x:t>ACSEL</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,7 +35,25 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>DUNYH</x:t>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
@@ -44,40 +62,148 @@
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDZA</x:t>
   </x:si>
   <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>TCKRC</x:t>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -428,7 +554,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -527,6 +653,270 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -544,7 +934,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -560,7 +950,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -571,7 +961,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -582,7 +972,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -593,7 +983,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -604,7 +994,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -615,7 +1005,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -626,7 +1016,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -637,12 +1027,210 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,61 +35,199 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
     <x:t>DGATE</x:t>
   </x:si>
   <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GESAN</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
+    <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>ICBCT</x:t>
   </x:si>
   <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
   </x:si>
   <x:si>
     <x:t>METRO</x:t>
@@ -98,112 +236,43 @@
     <x:t>MGROS</x:t>
   </x:si>
   <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
   </x:si>
   <x:si>
     <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -554,7 +623,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -906,17 +975,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -934,7 +992,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C27"/>
+  <x:dimension ref="A1:C51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -950,7 +1008,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -961,7 +1019,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -972,7 +1030,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -983,7 +1041,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -994,7 +1052,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1005,7 +1063,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1016,7 +1074,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,7 +1085,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1038,7 +1096,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1049,7 +1107,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1060,7 +1118,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1071,7 +1129,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1082,7 +1140,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1093,7 +1151,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1104,7 +1162,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1115,7 +1173,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1126,7 +1184,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1137,7 +1195,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1148,7 +1206,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1159,7 +1217,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1170,7 +1228,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1181,7 +1239,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1192,7 +1250,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1203,7 +1261,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1214,7 +1272,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1225,12 +1283,276 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,37 +26,145 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACSEL</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
   </x:si>
   <x:si>
     <x:t>AYES</x:t>
   </x:si>
   <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
     <x:t>BARMA</x:t>
   </x:si>
   <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
   </x:si>
   <x:si>
     <x:t>DURDO</x:t>
   </x:si>
   <x:si>
-    <x:t>DURKN</x:t>
+    <x:t>DZGYO</x:t>
   </x:si>
   <x:si>
     <x:t>EBEBK</x:t>
@@ -65,208 +173,130 @@
     <x:t>EGEPO</x:t>
   </x:si>
   <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
     <x:t>IZENR</x:t>
   </x:si>
   <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>KAREL</x:t>
   </x:si>
   <x:si>
     <x:t>KARSN</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
   </x:si>
   <x:si>
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
-    <x:t>TCKRC</x:t>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TEZOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
+    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
@@ -623,7 +653,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -843,138 +873,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -992,7 +890,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C51"/>
+  <x:dimension ref="A1:C73"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1008,7 +906,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1019,7 +917,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1030,7 +928,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1041,7 +939,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1052,7 +950,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1063,7 +961,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1074,7 +972,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1085,7 +983,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1096,7 +994,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1107,7 +1005,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1118,7 +1016,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1129,7 +1027,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1140,7 +1038,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1151,7 +1049,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1162,7 +1060,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1173,7 +1071,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1184,7 +1082,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1195,7 +1093,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1206,7 +1104,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1217,7 +1115,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1228,7 +1126,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1239,7 +1137,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1250,7 +1148,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1261,7 +1159,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1272,7 +1170,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1283,7 +1181,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1294,7 +1192,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1305,7 +1203,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1316,7 +1214,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1327,7 +1225,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1338,7 +1236,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1349,7 +1247,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1360,7 +1258,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1371,7 +1269,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1382,7 +1280,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1393,7 +1291,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1404,7 +1302,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1415,7 +1313,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1426,7 +1324,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1437,7 +1335,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1448,7 +1346,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1459,7 +1357,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1470,7 +1368,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1481,7 +1379,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1492,7 +1390,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1503,7 +1401,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1514,7 +1412,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -1525,7 +1423,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -1536,7 +1434,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -1547,12 +1445,254 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:3">
+      <x:c r="A64" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:3">
+      <x:c r="A65" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:3">
+      <x:c r="A66" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:3">
+      <x:c r="A67" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:3">
+      <x:c r="A68" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:3">
+      <x:c r="A69" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:3">
+      <x:c r="A70" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:3">
+      <x:c r="A71" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:3">
+      <x:c r="A72" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:3">
+      <x:c r="A73" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,79 +35,142 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>CVKMD</x:t>
   </x:si>
   <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
     <x:t>FADE</x:t>
   </x:si>
   <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDZA</x:t>
   </x:si>
   <x:si>
     <x:t>GESAN</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBCT</x:t>
+    <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
     <x:t>MAALT</x:t>
   </x:si>
   <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIATK</x:t>
   </x:si>
   <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
-    <x:t>YGGYO</x:t>
+    <x:t>YUNSA</x:t>
   </x:si>
   <x:si>
     <x:t>ACSEL</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
   </x:si>
   <x:si>
     <x:t>AVPGY</x:t>
@@ -128,6 +191,9 @@
     <x:t>BRISA</x:t>
   </x:si>
   <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
     <x:t>BRMEN</x:t>
   </x:si>
   <x:si>
@@ -137,15 +203,6 @@
     <x:t>BURVA</x:t>
   </x:si>
   <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
     <x:t>DGATE</x:t>
   </x:si>
   <x:si>
@@ -155,9 +212,6 @@
     <x:t>DOFRB</x:t>
   </x:si>
   <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
     <x:t>DOKTA</x:t>
   </x:si>
   <x:si>
@@ -167,54 +221,45 @@
     <x:t>DZGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
     <x:t>EGEPO</x:t>
   </x:si>
   <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
     <x:t>EKOS</x:t>
   </x:si>
   <x:si>
     <x:t>EREGL</x:t>
   </x:si>
   <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
     <x:t>FONET</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
     <x:t>IHAAS</x:t>
   </x:si>
   <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
     <x:t>IZFAS</x:t>
   </x:si>
   <x:si>
@@ -224,37 +269,34 @@
     <x:t>KARSN</x:t>
   </x:si>
   <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>KMPUR</x:t>
   </x:si>
   <x:si>
-    <x:t>KORDS</x:t>
+    <x:t>KRPLS</x:t>
   </x:si>
   <x:si>
     <x:t>KRSTL</x:t>
   </x:si>
   <x:si>
-    <x:t>KTLEV</x:t>
+    <x:t>KRVGD</x:t>
   </x:si>
   <x:si>
     <x:t>KUVVA</x:t>
   </x:si>
   <x:si>
-    <x:t>MACKO</x:t>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
   </x:si>
   <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
-    <x:t>ODINE</x:t>
+    <x:t>NTGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>ORCAY</x:t>
@@ -272,37 +314,34 @@
     <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
+    <x:t>PNLSN</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SANEL</x:t>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
   </x:si>
   <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>VBTYZ</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
   </x:si>
   <x:si>
-    <x:t>YUNSA</x:t>
+    <x:t>YEOTK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -653,7 +692,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C20"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -873,6 +912,215 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -890,7 +1138,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C73"/>
+  <x:dimension ref="A1:C67"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -906,7 +1154,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -917,7 +1165,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -928,7 +1176,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -939,7 +1187,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -950,7 +1198,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -961,7 +1209,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -972,7 +1220,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -983,7 +1231,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -994,7 +1242,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1005,7 +1253,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1016,7 +1264,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,7 +1275,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1038,7 +1286,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1049,7 +1297,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1060,7 +1308,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1071,7 +1319,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1082,7 +1330,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1093,7 +1341,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1104,7 +1352,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1115,7 +1363,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1126,7 +1374,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1137,7 +1385,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1148,7 +1396,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1159,7 +1407,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1170,7 +1418,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1181,7 +1429,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1192,7 +1440,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1203,7 +1451,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1214,7 +1462,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1225,7 +1473,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1236,7 +1484,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1247,7 +1495,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1258,7 +1506,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1269,7 +1517,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1280,7 +1528,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1291,7 +1539,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1302,7 +1550,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1313,7 +1561,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1324,7 +1572,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1335,7 +1583,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1346,7 +1594,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1357,7 +1605,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1368,7 +1616,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1379,7 +1627,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1390,7 +1638,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1401,7 +1649,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1412,7 +1660,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -1423,7 +1671,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -1434,7 +1682,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -1445,7 +1693,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -1456,7 +1704,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -1467,7 +1715,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -1478,7 +1726,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -1489,7 +1737,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -1500,7 +1748,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -1511,7 +1759,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -1522,7 +1770,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -1533,7 +1781,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -1544,7 +1792,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -1555,7 +1803,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -1566,7 +1814,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -1577,7 +1825,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -1588,7 +1836,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -1599,7 +1847,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -1610,7 +1858,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -1621,78 +1869,12 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:3">
-      <x:c r="A68" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:3">
-      <x:c r="A69" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:3">
-      <x:c r="A70" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:3">
-      <x:c r="A71" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:3">
-      <x:c r="A72" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:3">
-      <x:c r="A73" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,295 +26,379 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
     <x:t>CVKMD</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
   </x:si>
   <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
   </x:si>
   <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMA</x:t>
+    <x:t>KMPUR</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
   </x:si>
   <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
+    <x:t>PKART</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
@@ -326,22 +410,31 @@
     <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
     <x:t>SUMAS</x:t>
   </x:si>
   <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZEDUR</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -692,7 +785,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C39"/>
+  <x:dimension ref="A1:C62"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1121,6 +1214,259 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1138,7 +1484,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C67"/>
+  <x:dimension ref="A1:C75"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1154,7 +1500,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1165,7 +1511,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1176,7 +1522,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1187,7 +1533,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1198,7 +1544,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1209,7 +1555,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1220,7 +1566,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1231,7 +1577,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1242,7 +1588,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1253,7 +1599,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1264,7 +1610,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1275,7 +1621,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1286,7 +1632,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1297,7 +1643,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1308,7 +1654,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1319,7 +1665,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1330,7 +1676,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1341,7 +1687,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1352,7 +1698,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1363,7 +1709,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1374,7 +1720,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1385,7 +1731,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1396,7 +1742,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1407,7 +1753,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1418,7 +1764,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1429,7 +1775,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1440,7 +1786,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1451,7 +1797,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1462,7 +1808,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1473,7 +1819,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1484,7 +1830,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1495,7 +1841,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1506,7 +1852,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1517,7 +1863,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1528,7 +1874,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1539,7 +1885,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1550,7 +1896,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1561,7 +1907,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1572,7 +1918,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1583,7 +1929,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1594,7 +1940,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1605,7 +1951,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1616,7 +1962,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1627,7 +1973,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1638,7 +1984,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1649,7 +1995,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1660,7 +2006,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -1671,7 +2017,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -1682,7 +2028,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -1693,7 +2039,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -1704,7 +2050,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -1715,7 +2061,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -1726,7 +2072,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -1737,7 +2083,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -1748,7 +2094,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -1759,7 +2105,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -1770,7 +2116,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -1781,7 +2127,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -1792,7 +2138,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -1803,7 +2149,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -1814,7 +2160,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -1825,7 +2171,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -1836,7 +2182,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -1847,7 +2193,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -1858,7 +2204,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -1869,12 +2215,100 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:3">
+      <x:c r="A68" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:3">
+      <x:c r="A69" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:3">
+      <x:c r="A70" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:3">
+      <x:c r="A71" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:3">
+      <x:c r="A72" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:3">
+      <x:c r="A73" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:3">
+      <x:c r="A74" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:3">
+      <x:c r="A75" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>ACSEL</x:t>
+    <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,166 +35,310 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
+    <x:t>ALARK</x:t>
   </x:si>
   <x:si>
     <x:t>AYES</x:t>
   </x:si>
   <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
   </x:si>
   <x:si>
     <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
-    <x:t>EKSUN</x:t>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
   </x:si>
   <x:si>
     <x:t>EREGL</x:t>
   </x:si>
   <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -203,229 +347,7 @@
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
   </x:si>
   <x:si>
     <x:t>VKGYO</x:t>
@@ -785,7 +707,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C62"/>
+  <x:dimension ref="A1:C61"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1456,17 +1378,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1484,7 +1395,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C75"/>
+  <x:dimension ref="A1:C50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1500,7 +1411,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1511,7 +1422,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1522,7 +1433,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1533,7 +1444,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1544,7 +1455,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1555,7 +1466,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1566,7 +1477,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1577,7 +1488,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1588,7 +1499,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1599,7 +1510,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1610,7 +1521,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1621,7 +1532,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1632,7 +1543,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1643,7 +1554,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1654,7 +1565,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1665,7 +1576,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1676,7 +1587,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1687,7 +1598,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1698,7 +1609,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1709,7 +1620,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1720,7 +1631,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1731,7 +1642,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1742,7 +1653,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1753,7 +1664,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1764,7 +1675,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1775,7 +1686,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1786,7 +1697,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1797,7 +1708,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1808,7 +1719,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1819,7 +1730,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1830,7 +1741,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1841,7 +1752,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1852,7 +1763,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1863,7 +1774,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1874,7 +1785,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1885,7 +1796,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1896,7 +1807,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1907,7 +1818,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1918,7 +1829,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1929,7 +1840,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1940,7 +1851,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1951,7 +1862,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1962,7 +1873,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1973,7 +1884,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1984,7 +1895,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1995,7 +1906,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -2006,7 +1917,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -2017,7 +1928,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -2028,287 +1939,12 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:3">
-      <x:c r="A63" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:3">
-      <x:c r="A64" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:3">
-      <x:c r="A65" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:3">
-      <x:c r="A66" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:3">
-      <x:c r="A67" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:3">
-      <x:c r="A68" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:3">
-      <x:c r="A69" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:3">
-      <x:c r="A70" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:3">
-      <x:c r="A71" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:3">
-      <x:c r="A72" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:3">
-      <x:c r="A73" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:3">
-      <x:c r="A74" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:3">
-      <x:c r="A75" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,334 +26,286 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARASE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
   </x:si>
   <x:si>
     <x:t>ESCAR</x:t>
   </x:si>
   <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
   </x:si>
   <x:si>
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PNLSN</x:t>
   </x:si>
   <x:si>
     <x:t>PRKAB</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
+    <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>VERUS</x:t>
   </x:si>
   <x:si>
     <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
   </x:si>
   <x:si>
     <x:t>ZEDUR</x:t>
@@ -707,7 +659,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C61"/>
+  <x:dimension ref="A1:C47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1224,160 +1176,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1395,7 +1193,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C50"/>
+  <x:dimension ref="A1:C48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1411,7 +1209,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1422,7 +1220,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1433,7 +1231,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1444,7 +1242,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1455,7 +1253,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1466,7 +1264,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1477,7 +1275,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1488,7 +1286,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1499,7 +1297,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1510,7 +1308,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1521,7 +1319,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1532,7 +1330,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1543,7 +1341,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1554,7 +1352,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1565,7 +1363,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1576,7 +1374,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1587,7 +1385,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1598,7 +1396,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1609,7 +1407,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1620,7 +1418,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1631,7 +1429,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1642,7 +1440,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1653,7 +1451,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1664,7 +1462,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1675,7 +1473,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1686,7 +1484,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1697,7 +1495,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1708,7 +1506,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1719,7 +1517,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1730,7 +1528,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1741,7 +1539,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1752,7 +1550,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1763,7 +1561,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1774,7 +1572,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1785,7 +1583,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1796,7 +1594,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1807,7 +1605,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1818,7 +1616,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1829,7 +1627,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1840,7 +1638,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1851,7 +1649,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1862,7 +1660,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1873,7 +1671,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1884,7 +1682,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1895,7 +1693,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1906,7 +1704,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1917,34 +1715,12 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,234 +26,207 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AEFES</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>ATAKP</x:t>
   </x:si>
   <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
   </x:si>
   <x:si>
     <x:t>DGATE</x:t>
   </x:si>
   <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
     <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
     <x:t>IZMDC</x:t>
   </x:si>
   <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
@@ -269,30 +242,24 @@
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
+    <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
@@ -303,9 +270,6 @@
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
   </x:si>
   <x:si>
     <x:t>ZEDUR</x:t>
@@ -659,7 +623,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C47"/>
+  <x:dimension ref="A1:C41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1110,72 +1074,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1193,7 +1091,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C48"/>
+  <x:dimension ref="A1:C42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1209,7 +1107,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1220,7 +1118,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1231,7 +1129,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1242,7 +1140,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1253,7 +1151,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1264,7 +1162,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1275,7 +1173,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1286,7 +1184,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1297,7 +1195,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1308,7 +1206,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1319,7 +1217,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1330,7 +1228,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1341,7 +1239,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1352,7 +1250,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1363,7 +1261,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1374,7 +1272,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1385,7 +1283,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1396,7 +1294,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1407,7 +1305,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1418,7 +1316,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1429,7 +1327,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1440,7 +1338,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1451,7 +1349,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1462,7 +1360,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1473,7 +1371,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1484,7 +1382,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1495,7 +1393,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1506,7 +1404,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1517,7 +1415,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1528,7 +1426,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1539,7 +1437,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1550,7 +1448,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1561,7 +1459,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1572,7 +1470,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1583,7 +1481,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1594,7 +1492,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1605,7 +1503,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1616,7 +1514,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1627,7 +1525,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1638,7 +1536,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1649,78 +1547,12 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -41,10 +41,25 @@
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
-    <x:t>BYDNR</x:t>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
@@ -56,10 +71,7 @@
     <x:t>CUSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
+    <x:t>DZGYO</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
@@ -71,192 +83,207 @@
     <x:t>EUYO</x:t>
   </x:si>
   <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARFA</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GESAN</x:t>
   </x:si>
   <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
+    <x:t>SMART</x:t>
   </x:si>
   <x:si>
     <x:t>SURGY</x:t>
   </x:si>
   <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
@@ -266,10 +293,10 @@
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
   </x:si>
   <x:si>
     <x:t>ZEDUR</x:t>
@@ -623,7 +650,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C41"/>
+  <x:dimension ref="A1:C46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1074,6 +1101,61 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1091,7 +1173,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C42"/>
+  <x:dimension ref="A1:C46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1107,7 +1189,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1118,7 +1200,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1129,7 +1211,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1140,7 +1222,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1151,7 +1233,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1162,7 +1244,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1173,7 +1255,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1184,7 +1266,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1195,7 +1277,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1206,7 +1288,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1217,7 +1299,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1228,7 +1310,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1239,7 +1321,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1250,7 +1332,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1261,7 +1343,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1272,7 +1354,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1283,7 +1365,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1294,7 +1376,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1305,7 +1387,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1316,7 +1398,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1327,7 +1409,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1338,7 +1420,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1349,7 +1431,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1360,7 +1442,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1371,7 +1453,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1382,7 +1464,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1393,7 +1475,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1404,7 +1486,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1415,7 +1497,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1426,7 +1508,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1437,7 +1519,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1448,7 +1530,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1459,7 +1541,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1470,7 +1552,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1481,7 +1563,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1492,7 +1574,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1503,7 +1585,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1514,7 +1596,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1525,7 +1607,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1536,7 +1618,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1547,12 +1629,56 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,7 +35,7 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AKENR</x:t>
+    <x:t>AGESA</x:t>
   </x:si>
   <x:si>
     <x:t>AKFYE</x:t>
@@ -44,10 +44,13 @@
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
   </x:si>
   <x:si>
     <x:t>ATSYH</x:t>
@@ -56,250 +59,220 @@
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BARMA</x:t>
   </x:si>
   <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
     <x:t>BRLSM</x:t>
   </x:si>
   <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUYO</x:t>
   </x:si>
   <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
   </x:si>
   <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
     <x:t>SUMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
     <x:t>SURGY</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZEDUR</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -650,7 +623,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C46"/>
+  <x:dimension ref="A1:C48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1156,6 +1129,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1173,7 +1168,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C46"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1189,7 +1184,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1200,7 +1195,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1211,7 +1206,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1222,7 +1217,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1233,7 +1228,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1244,7 +1239,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1255,7 +1250,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1266,7 +1261,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1277,7 +1272,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1288,7 +1283,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1299,7 +1294,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1310,7 +1305,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1321,7 +1316,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1332,7 +1327,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1343,7 +1338,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1354,7 +1349,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1365,7 +1360,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1376,7 +1371,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1387,7 +1382,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1398,7 +1393,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1409,7 +1404,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1420,7 +1415,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1431,7 +1426,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1442,7 +1437,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1453,7 +1448,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1464,7 +1459,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1475,7 +1470,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1486,7 +1481,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1497,7 +1492,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1508,7 +1503,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1519,7 +1514,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1530,7 +1525,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1541,7 +1536,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1552,133 +1547,12 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>A1YEN</x:t>
+    <x:t>AGESA</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,244 +35,178 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
     <x:t>ALARK</x:t>
   </x:si>
   <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
   </x:si>
   <x:si>
     <x:t>KGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
     <x:t>MARKA</x:t>
   </x:si>
   <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
+    <x:t>YUNSA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -623,7 +557,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C48"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -986,171 +920,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1168,7 +937,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1184,7 +953,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1195,7 +964,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1206,7 +975,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1217,7 +986,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1228,7 +997,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1239,7 +1008,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1250,7 +1019,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1261,7 +1030,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1272,7 +1041,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1283,7 +1052,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1294,7 +1063,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1305,7 +1074,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1316,7 +1085,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1327,7 +1096,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1338,7 +1107,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1349,7 +1118,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1360,7 +1129,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1371,7 +1140,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1382,7 +1151,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1393,7 +1162,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1404,7 +1173,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1415,7 +1184,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1426,7 +1195,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1437,7 +1206,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1448,7 +1217,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1459,7 +1228,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1470,89 +1239,12 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,138 +26,138 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
@@ -167,21 +167,39 @@
     <x:t>KGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
     <x:t>KOPOL</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARKA</x:t>
   </x:si>
   <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
@@ -191,10 +209,10 @@
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
@@ -557,7 +575,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -909,17 +927,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -937,7 +944,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C28"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -953,7 +960,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -964,7 +971,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -975,7 +982,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -986,7 +993,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -997,7 +1004,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1008,7 +1015,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1019,7 +1026,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1030,7 +1037,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1041,7 +1048,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1052,7 +1059,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1063,7 +1070,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1074,7 +1081,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1085,7 +1092,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1096,7 +1103,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1107,7 +1114,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1118,7 +1125,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1129,7 +1136,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1140,7 +1147,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1151,7 +1158,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1162,7 +1169,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1173,7 +1180,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1184,7 +1191,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1195,7 +1202,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1206,7 +1213,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1217,7 +1224,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1228,7 +1235,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1239,12 +1246,89 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,153 +26,180 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALARK</x:t>
   </x:si>
   <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
     <x:t>ECOGR</x:t>
   </x:si>
   <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
@@ -188,24 +215,24 @@
     <x:t>MEGMT</x:t>
   </x:si>
   <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
+    <x:t>OBASE</x:t>
   </x:si>
   <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
@@ -215,13 +242,25 @@
     <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
   </x:si>
   <x:si>
     <x:t>YUNSA</x:t>
@@ -575,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -927,6 +966,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -944,7 +1027,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -960,7 +1043,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -971,7 +1054,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -982,7 +1065,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -993,7 +1076,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1004,7 +1087,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1015,7 +1098,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1026,7 +1109,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1037,7 +1120,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1048,7 +1131,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1059,7 +1142,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1070,7 +1153,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1081,7 +1164,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1092,7 +1175,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1103,7 +1186,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1114,7 +1197,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1125,7 +1208,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1136,7 +1219,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1147,7 +1230,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1158,7 +1241,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1169,7 +1252,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1180,7 +1263,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1191,7 +1274,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1202,7 +1285,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1213,7 +1296,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1224,7 +1307,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1235,7 +1318,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1246,7 +1329,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1257,7 +1340,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1268,7 +1351,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1279,7 +1362,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1290,7 +1373,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1301,7 +1384,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1312,7 +1395,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1323,12 +1406,111 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,169 +26,235 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AEFES</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
   </x:si>
   <x:si>
     <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>CEMZY</x:t>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
   </x:si>
   <x:si>
     <x:t>ERSU</x:t>
   </x:si>
   <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
@@ -200,15 +266,24 @@
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARKA</x:t>
   </x:si>
   <x:si>
@@ -218,6 +293,9 @@
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>OBASE</x:t>
   </x:si>
   <x:si>
@@ -230,25 +308,34 @@
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>SKBNK</x:t>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
   </x:si>
   <x:si>
     <x:t>SURGY</x:t>
   </x:si>
   <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TLMAN</x:t>
@@ -257,10 +344,10 @@
     <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
   </x:si>
   <x:si>
     <x:t>YUNSA</x:t>
@@ -614,7 +701,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1010,6 +1097,149 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1027,7 +1257,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C60"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1043,7 +1273,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1054,7 +1284,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1065,7 +1295,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1076,7 +1306,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1087,7 +1317,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1098,7 +1328,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1109,7 +1339,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1120,7 +1350,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1131,7 +1361,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1142,7 +1372,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1153,7 +1383,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1164,7 +1394,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1175,7 +1405,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1186,7 +1416,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1197,7 +1427,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1208,7 +1438,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1219,7 +1449,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1230,7 +1460,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1241,7 +1471,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1252,7 +1482,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1263,7 +1493,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1274,7 +1504,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1285,7 +1515,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1296,7 +1526,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1307,7 +1537,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1318,7 +1548,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1329,7 +1559,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1340,7 +1570,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1351,7 +1581,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1362,7 +1592,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1373,7 +1603,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1384,7 +1614,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1395,7 +1625,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1406,7 +1636,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1417,7 +1647,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1428,7 +1658,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1439,7 +1669,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1450,7 +1680,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1461,7 +1691,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1472,7 +1702,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1483,7 +1713,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1494,7 +1724,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1505,12 +1735,188 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,303 +35,276 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
     <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
   </x:si>
   <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
+    <x:t>KOPOL</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMA</x:t>
   </x:si>
   <x:si>
-    <x:t>LILAK</x:t>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
-    <x:t>MEPET</x:t>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
   </x:si>
   <x:si>
     <x:t>MGROS</x:t>
   </x:si>
   <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
   </x:si>
   <x:si>
     <x:t>ODAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SELEC</x:t>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
   </x:si>
   <x:si>
     <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
@@ -341,13 +314,10 @@
     <x:t>TLMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKKO</x:t>
+    <x:t>YEOTK</x:t>
   </x:si>
   <x:si>
     <x:t>YUNSA</x:t>
@@ -701,7 +671,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C49"/>
+  <x:dimension ref="A1:C51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1240,6 +1210,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1257,7 +1249,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C60"/>
+  <x:dimension ref="A1:C48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1273,7 +1265,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1276,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1287,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1306,7 +1298,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1317,7 +1309,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1328,7 +1320,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1339,7 +1331,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1350,7 +1342,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1361,7 +1353,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1372,7 +1364,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1383,7 +1375,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1394,7 +1386,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1405,7 +1397,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1416,7 +1408,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1427,7 +1419,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1438,7 +1430,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1449,7 +1441,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1460,7 +1452,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1471,7 +1463,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1482,7 +1474,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1493,7 +1485,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1504,7 +1496,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1515,7 +1507,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1526,7 +1518,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1537,7 +1529,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1548,7 +1540,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1559,7 +1551,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1570,7 +1562,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1581,7 +1573,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1592,7 +1584,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1603,7 +1595,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1614,7 +1606,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1625,7 +1617,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1636,7 +1628,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1647,7 +1639,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1658,7 +1650,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1669,7 +1661,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1680,7 +1672,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1691,7 +1683,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1702,7 +1694,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1713,7 +1705,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1724,7 +1716,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1735,7 +1727,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1746,7 +1738,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1757,7 +1749,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1768,7 +1760,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1779,144 +1771,12 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,301 +26,274 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
     <x:t>BARMA</x:t>
   </x:si>
   <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
     <x:t>CVKMD</x:t>
   </x:si>
   <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
   </x:si>
   <x:si>
     <x:t>DOCO</x:t>
   </x:si>
   <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TLMAN</x:t>
   </x:si>
   <x:si>
     <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
+    <x:t>YKBNK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -671,7 +644,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C51"/>
+  <x:dimension ref="A1:C42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1133,105 +1106,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1265,7 +1139,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1276,7 +1150,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1287,7 +1161,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1298,7 +1172,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1309,7 +1183,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1320,7 +1194,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1331,7 +1205,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1342,7 +1216,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1353,7 +1227,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1364,7 +1238,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1375,7 +1249,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1386,7 +1260,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1397,7 +1271,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1408,7 +1282,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1419,7 +1293,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1430,7 +1304,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1441,7 +1315,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1452,7 +1326,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1463,7 +1337,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1474,7 +1348,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1485,7 +1359,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1496,7 +1370,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1507,7 +1381,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1518,7 +1392,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1529,7 +1403,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1540,7 +1414,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1551,7 +1425,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1562,7 +1436,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1573,7 +1447,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1584,7 +1458,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1595,7 +1469,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1606,7 +1480,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1617,7 +1491,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1628,7 +1502,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1639,7 +1513,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1650,7 +1524,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1661,7 +1535,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1672,7 +1546,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1683,7 +1557,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1694,7 +1568,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1705,7 +1579,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1716,7 +1590,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1727,7 +1601,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1738,7 +1612,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1749,7 +1623,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1760,7 +1634,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1771,7 +1645,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,7 +38,7 @@
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSUE</x:t>
+    <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
     <x:t>ALCTL</x:t>
@@ -50,247 +50,310 @@
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
   </x:si>
   <x:si>
     <x:t>DITAS</x:t>
   </x:si>
   <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
     <x:t>KAPLM</x:t>
   </x:si>
   <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
-    <x:t>SELEC</x:t>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>TLMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUSE</x:t>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
@@ -644,7 +707,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C42"/>
+  <x:dimension ref="A1:C43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1106,6 +1169,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1123,7 +1197,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C48"/>
+  <x:dimension ref="A1:C68"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1139,7 +1213,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1150,7 +1224,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1161,7 +1235,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1172,7 +1246,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1183,7 +1257,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1194,7 +1268,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1205,7 +1279,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1216,7 +1290,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1227,7 +1301,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1238,7 +1312,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1249,7 +1323,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1260,7 +1334,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1271,7 +1345,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1282,7 +1356,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1293,7 +1367,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1304,7 +1378,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1315,7 +1389,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1326,7 +1400,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1337,7 +1411,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1348,7 +1422,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1359,7 +1433,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1370,7 +1444,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1381,7 +1455,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1392,7 +1466,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1403,7 +1477,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1414,7 +1488,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1425,7 +1499,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1436,7 +1510,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1447,7 +1521,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1458,7 +1532,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1469,7 +1543,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1480,7 +1554,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1491,7 +1565,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1502,7 +1576,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1513,7 +1587,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1524,7 +1598,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1535,7 +1609,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1546,7 +1620,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1557,7 +1631,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1568,7 +1642,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1579,7 +1653,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1590,7 +1664,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1601,7 +1675,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1612,7 +1686,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1623,7 +1697,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1634,7 +1708,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1645,12 +1719,232 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:3">
+      <x:c r="A64" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:3">
+      <x:c r="A65" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:3">
+      <x:c r="A66" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:3">
+      <x:c r="A67" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:3">
+      <x:c r="A68" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,334 +26,292 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
   </x:si>
   <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
   </x:si>
   <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
   </x:si>
   <x:si>
     <x:t>TOASO</x:t>
   </x:si>
   <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKBN</x:t>
   </x:si>
   <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
     <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
@@ -707,7 +665,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C43"/>
+  <x:dimension ref="A1:C45"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1180,6 +1138,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1197,7 +1177,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C68"/>
+  <x:dimension ref="A1:C52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1213,7 +1193,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1224,7 +1204,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1235,7 +1215,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1246,7 +1226,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1257,7 +1237,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1268,7 +1248,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1279,7 +1259,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1290,7 +1270,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1301,7 +1281,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1312,7 +1292,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1323,7 +1303,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1334,7 +1314,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1345,7 +1325,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1356,7 +1336,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1367,7 +1347,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1378,7 +1358,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1389,7 +1369,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1400,7 +1380,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1411,7 +1391,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1422,7 +1402,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1433,7 +1413,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1444,7 +1424,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1455,7 +1435,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1466,7 +1446,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1477,7 +1457,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1488,7 +1468,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1499,7 +1479,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1510,7 +1490,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1521,7 +1501,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1532,7 +1512,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1543,7 +1523,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1554,7 +1534,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1565,7 +1545,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1576,7 +1556,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1587,7 +1567,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1598,7 +1578,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1609,7 +1589,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1620,7 +1600,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1631,7 +1611,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1642,7 +1622,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1653,7 +1633,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1664,7 +1644,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1675,7 +1655,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1686,7 +1666,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1697,7 +1677,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1708,7 +1688,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1719,7 +1699,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -1730,7 +1710,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -1741,7 +1721,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -1752,7 +1732,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -1763,188 +1743,12 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:3">
-      <x:c r="A63" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:3">
-      <x:c r="A64" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:3">
-      <x:c r="A65" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:3">
-      <x:c r="A66" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:3">
-      <x:c r="A67" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:3">
-      <x:c r="A68" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,91 +26,247 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
   </x:si>
   <x:si>
     <x:t>GEREL</x:t>
   </x:si>
   <x:si>
-    <x:t>GLBMD</x:t>
+    <x:t>GESAN</x:t>
   </x:si>
   <x:si>
     <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
+    <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>HATSN</x:t>
   </x:si>
   <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
     <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
   </x:si>
   <x:si>
     <x:t>ISCTR</x:t>
   </x:si>
   <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>KRPLS</x:t>
@@ -119,199 +275,61 @@
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>LUKSK</x:t>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
   </x:si>
   <x:si>
     <x:t>MTRKS</x:t>
   </x:si>
   <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>NETAS</x:t>
   </x:si>
   <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>THYAO</x:t>
   </x:si>
   <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRALT</x:t>
   </x:si>
   <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
     <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
@@ -665,7 +683,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C45"/>
+  <x:dimension ref="A1:C40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1105,61 +1123,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1177,7 +1140,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C52"/>
+  <x:dimension ref="A1:C63"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1193,7 +1156,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1204,7 +1167,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1215,7 +1178,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1226,7 +1189,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1237,7 +1200,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1248,7 +1211,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1259,7 +1222,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1270,7 +1233,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1281,7 +1244,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1292,7 +1255,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1303,7 +1266,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1314,7 +1277,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1325,7 +1288,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1336,7 +1299,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1347,7 +1310,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1358,7 +1321,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1369,7 +1332,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1380,7 +1343,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1391,7 +1354,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1402,7 +1365,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1413,7 +1376,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1424,7 +1387,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1435,7 +1398,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1446,7 +1409,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1457,7 +1420,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1468,7 +1431,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1479,7 +1442,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1490,7 +1453,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1501,7 +1464,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1512,7 +1475,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1523,7 +1486,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1534,7 +1497,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1545,7 +1508,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1556,7 +1519,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1567,7 +1530,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1578,7 +1541,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1589,7 +1552,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1600,7 +1563,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1611,7 +1574,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1622,7 +1585,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1633,7 +1596,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1644,7 +1607,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1655,7 +1618,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1666,7 +1629,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1677,7 +1640,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1688,7 +1651,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -1699,7 +1662,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -1710,7 +1673,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -1721,7 +1684,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -1732,7 +1695,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -1743,12 +1706,133 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>ANSGR</x:t>
+    <x:t>AKENR</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,28 +35,130 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
     <x:t>ASGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
   </x:si>
   <x:si>
     <x:t>DOFRB</x:t>
@@ -65,13 +167,10 @@
     <x:t>DSTKF</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
@@ -83,52 +182,67 @@
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
   </x:si>
   <x:si>
     <x:t>IZMDC</x:t>
   </x:si>
   <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>LUKSK</x:t>
   </x:si>
   <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
   </x:si>
   <x:si>
     <x:t>SELEC</x:t>
@@ -137,199 +251,19 @@
     <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
     <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
@@ -683,7 +617,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C40"/>
+  <x:dimension ref="A1:C34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1057,72 +991,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1140,7 +1008,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C63"/>
+  <x:dimension ref="A1:C47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1156,7 +1024,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1167,7 +1035,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1178,7 +1046,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1189,7 +1057,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1200,7 +1068,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1211,7 +1079,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1222,7 +1090,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1233,7 +1101,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1244,7 +1112,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1255,7 +1123,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1266,7 +1134,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1277,7 +1145,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1288,7 +1156,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1299,7 +1167,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1310,7 +1178,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1321,7 +1189,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1332,7 +1200,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1343,7 +1211,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1354,7 +1222,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1365,7 +1233,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1376,7 +1244,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1387,7 +1255,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1398,7 +1266,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1409,7 +1277,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1420,7 +1288,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1431,7 +1299,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1442,7 +1310,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1453,7 +1321,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1464,7 +1332,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1475,7 +1343,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1486,7 +1354,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1497,7 +1365,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1508,7 +1376,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1519,7 +1387,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1530,7 +1398,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1541,7 +1409,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1552,7 +1420,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1563,7 +1431,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1574,7 +1442,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1585,7 +1453,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1596,7 +1464,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1607,7 +1475,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1618,7 +1486,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -1629,7 +1497,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -1640,7 +1508,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -1651,188 +1519,12 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:3">
-      <x:c r="A63" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AKENR</x:t>
+    <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -38,232 +38,205 @@
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
   </x:si>
   <x:si>
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
   </x:si>
   <x:si>
     <x:t>ESCOM</x:t>
   </x:si>
   <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
     <x:t>GLBMD</x:t>
   </x:si>
   <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
     <x:t>HATSN</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
@@ -617,7 +590,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C34"/>
+  <x:dimension ref="A1:C28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -925,72 +898,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1008,7 +915,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C47"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1024,7 +931,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1035,7 +942,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1046,7 +953,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1057,7 +964,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1068,7 +975,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1079,7 +986,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1090,7 +997,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1101,7 +1008,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1112,7 +1019,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1123,7 +1030,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1134,7 +1041,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1145,7 +1052,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1156,7 +1063,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1167,7 +1074,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1178,7 +1085,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1189,7 +1096,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1200,7 +1107,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1211,7 +1118,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1222,7 +1129,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1233,7 +1140,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1244,7 +1151,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1255,7 +1162,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1266,7 +1173,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1277,7 +1184,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1288,7 +1195,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1299,7 +1206,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1310,7 +1217,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1321,7 +1228,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1332,7 +1239,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1343,7 +1250,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1354,7 +1261,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1365,7 +1272,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1376,7 +1283,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1387,7 +1294,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1398,7 +1305,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1409,7 +1316,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1420,7 +1327,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1431,7 +1338,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1442,7 +1349,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1453,7 +1360,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1464,7 +1371,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1475,7 +1382,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1486,45 +1393,12 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,34 +35,127 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>IEYHO</x:t>
@@ -71,175 +164,55 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
+    <x:t>KARSN</x:t>
   </x:si>
   <x:si>
     <x:t>KARTN</x:t>
   </x:si>
   <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
   </x:si>
   <x:si>
     <x:t>SANEL</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKUR</x:t>
+    <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKBNK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -590,7 +563,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C28"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -898,6 +871,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -915,7 +899,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -931,7 +915,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -942,7 +926,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -953,7 +937,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -964,7 +948,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -975,7 +959,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -986,7 +970,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -997,7 +981,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1008,7 +992,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1019,7 +1003,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1030,7 +1014,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1041,7 +1025,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1052,7 +1036,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1063,7 +1047,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1074,7 +1058,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1085,7 +1069,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1096,7 +1080,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1107,7 +1091,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1118,7 +1102,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1129,7 +1113,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1140,7 +1124,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1151,7 +1135,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1162,7 +1146,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1173,7 +1157,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1184,7 +1168,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1195,7 +1179,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1206,7 +1190,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1217,7 +1201,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1228,7 +1212,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1239,7 +1223,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1250,7 +1234,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1261,7 +1245,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1272,7 +1256,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1283,122 +1267,12 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,190 +26,178 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
-    <x:t>BRMEN</x:t>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
     <x:t>DOCO</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>IZFAS</x:t>
   </x:si>
   <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
   </x:si>
   <x:si>
     <x:t>OZSUB</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TRGYO</x:t>
@@ -563,7 +551,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C29"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -816,72 +804,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -899,7 +821,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C34"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -915,7 +837,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -926,7 +848,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -937,7 +859,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -948,7 +870,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -959,7 +881,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -970,7 +892,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -981,7 +903,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -992,7 +914,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1003,7 +925,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1014,7 +936,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1025,7 +947,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1036,7 +958,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1047,7 +969,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1058,7 +980,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1069,7 +991,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1080,7 +1002,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1091,7 +1013,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1102,7 +1024,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1113,7 +1035,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1124,7 +1046,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1135,7 +1057,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1146,7 +1068,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1157,7 +1079,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1168,7 +1090,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1179,7 +1101,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1190,7 +1112,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1201,7 +1123,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1212,7 +1134,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1223,7 +1145,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1234,7 +1156,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1245,7 +1167,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1256,7 +1178,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1267,12 +1189,34 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,163 +35,172 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
+    <x:t>ASGYO</x:t>
   </x:si>
   <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
     <x:t>ECOGR</x:t>
   </x:si>
   <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
     <x:t>IDGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
   </x:si>
   <x:si>
     <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKUR</x:t>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
@@ -551,7 +560,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -749,61 +758,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -821,7 +775,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -837,7 +791,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -848,7 +802,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -859,7 +813,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -870,7 +824,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -881,7 +835,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -892,7 +846,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -903,7 +857,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -914,7 +868,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -925,7 +879,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -936,7 +890,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -947,7 +901,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -958,7 +912,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -969,7 +923,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -980,7 +934,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -991,7 +945,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1002,7 +956,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1013,7 +967,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1024,7 +978,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1035,7 +989,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1046,7 +1000,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1057,7 +1011,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1068,7 +1022,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1079,7 +1033,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1090,7 +1044,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1101,7 +1055,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1112,7 +1066,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1123,7 +1077,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1134,7 +1088,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1145,7 +1099,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1156,7 +1110,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1167,7 +1121,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1178,7 +1132,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1189,7 +1143,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1200,7 +1154,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1211,12 +1165,100 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,16 +26,25 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
     <x:t>ATSYH</x:t>
@@ -44,16 +53,19 @@
     <x:t>AYES</x:t>
   </x:si>
   <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>BSOKE</x:t>
   </x:si>
   <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
   </x:si>
   <x:si>
     <x:t>GUNDG</x:t>
@@ -62,151 +74,151 @@
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
   </x:si>
   <x:si>
     <x:t>KARTN</x:t>
   </x:si>
   <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
     <x:t>KBORU</x:t>
   </x:si>
   <x:si>
-    <x:t>KRONT</x:t>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
   </x:si>
   <x:si>
     <x:t>OZKGY</x:t>
   </x:si>
   <x:si>
-    <x:t>OZYSR</x:t>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
   </x:si>
   <x:si>
     <x:t>TRGYO</x:t>
@@ -560,7 +572,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C18"/>
+  <x:dimension ref="A1:C27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -758,6 +770,105 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -775,7 +886,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -791,7 +902,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -802,7 +913,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -813,7 +924,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -824,7 +935,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -835,7 +946,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -846,7 +957,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -857,7 +968,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -868,7 +979,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -879,7 +990,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -890,7 +1001,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -901,7 +1012,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -912,7 +1023,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -923,7 +1034,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -934,7 +1045,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -945,7 +1056,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -956,7 +1067,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -967,7 +1078,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -978,7 +1089,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -989,7 +1100,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1000,7 +1111,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1011,7 +1122,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1022,7 +1133,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1033,7 +1144,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1044,7 +1155,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1055,7 +1166,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1066,7 +1177,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1077,7 +1188,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1088,7 +1199,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1099,7 +1210,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1110,7 +1221,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1121,7 +1232,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1132,7 +1243,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1143,7 +1254,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1154,7 +1265,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1165,7 +1276,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1176,7 +1287,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1187,7 +1298,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1198,67 +1309,12 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,190 +38,229 @@
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
     <x:t>AYES</x:t>
   </x:si>
   <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSOKE</x:t>
   </x:si>
   <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>GLBMD</x:t>
   </x:si>
   <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
   </x:si>
   <x:si>
     <x:t>KARTN</x:t>
   </x:si>
   <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
+    <x:t>UFUK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -572,7 +611,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C27"/>
+  <x:dimension ref="A1:C31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -869,6 +908,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -886,7 +969,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C39"/>
+  <x:dimension ref="A1:C48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -902,7 +985,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -913,7 +996,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -924,7 +1007,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -935,7 +1018,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -946,7 +1029,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -957,7 +1040,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -968,7 +1051,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -979,7 +1062,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -990,7 +1073,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1001,7 +1084,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1012,7 +1095,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1023,7 +1106,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1034,7 +1117,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1045,7 +1128,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1056,7 +1139,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1067,7 +1150,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1078,7 +1161,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1089,7 +1172,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1100,7 +1183,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1111,7 +1194,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1122,7 +1205,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1133,7 +1216,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1144,7 +1227,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1155,7 +1238,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1166,7 +1249,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1177,7 +1260,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1188,7 +1271,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1199,7 +1282,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1210,7 +1293,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1221,7 +1304,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1232,7 +1315,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1243,7 +1326,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1254,7 +1337,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1265,7 +1348,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1276,7 +1359,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1287,7 +1370,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1298,7 +1381,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1309,12 +1392,111 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,9 +35,6 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
@@ -47,16 +44,127 @@
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
-    <x:t>AYES</x:t>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
   </x:si>
   <x:si>
     <x:t>CCOLA</x:t>
   </x:si>
   <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
   </x:si>
   <x:si>
     <x:t>DSTKF</x:t>
@@ -65,202 +173,85 @@
     <x:t>DZGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
+    <x:t>ISGSY</x:t>
   </x:si>
   <x:si>
     <x:t>IZFAS</x:t>
   </x:si>
   <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -611,7 +602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C31"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -952,6 +943,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -969,7 +982,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C48"/>
+  <x:dimension ref="A1:C43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -985,7 +998,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -996,7 +1009,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1007,7 +1020,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1018,7 +1031,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1029,7 +1042,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1040,7 +1053,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1051,7 +1064,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1062,7 +1075,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1073,7 +1086,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1084,7 +1097,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1095,7 +1108,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1106,7 +1119,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1117,7 +1130,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1128,7 +1141,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1139,7 +1152,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1150,7 +1163,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1161,7 +1174,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1172,7 +1185,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1183,7 +1196,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1194,7 +1207,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1205,7 +1218,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1216,7 +1229,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1227,7 +1240,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1238,7 +1251,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1249,7 +1262,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1260,7 +1273,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1271,7 +1284,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1282,7 +1295,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1293,7 +1306,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1304,7 +1317,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1315,7 +1328,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1326,7 +1339,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1337,7 +1350,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1348,7 +1361,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1359,7 +1372,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1370,7 +1383,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1381,7 +1394,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1392,7 +1405,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1403,7 +1416,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1414,7 +1427,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1425,7 +1438,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1436,67 +1449,12 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AGHOL</x:t>
+    <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,16 +35,22 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARDYZ</x:t>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
     <x:t>BAKAB</x:t>
@@ -56,7 +62,7 @@
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
-    <x:t>DOFRB</x:t>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>DURKN</x:t>
@@ -65,7 +71,7 @@
     <x:t>EDIP</x:t>
   </x:si>
   <x:si>
-    <x:t>EREGL</x:t>
+    <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
@@ -74,184 +80,169 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
     <x:t>GSDHO</x:t>
   </x:si>
   <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
   </x:si>
   <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
   </x:si>
   <x:si>
     <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
     <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -602,7 +593,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -965,6 +956,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -982,7 +984,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C43"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -998,7 +1000,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1009,7 +1011,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1020,7 +1022,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1031,7 +1033,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1042,7 +1044,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1053,7 +1055,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1064,7 +1066,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1075,7 +1077,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1086,7 +1088,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1097,7 +1099,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1108,7 +1110,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1121,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1132,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1143,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1154,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1165,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1176,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1187,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1198,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1209,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1220,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1231,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1242,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1253,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1264,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1275,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1286,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1297,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1306,7 +1308,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1317,7 +1319,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1328,7 +1330,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1339,7 +1341,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1350,7 +1352,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1361,7 +1363,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1372,7 +1374,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1383,7 +1385,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1394,7 +1396,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1405,56 +1407,12 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,187 +35,181 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSA</x:t>
+    <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
   </x:si>
   <x:si>
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
-    <x:t>DUNYH</x:t>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
     <x:t>DURKN</x:t>
   </x:si>
   <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
   </x:si>
   <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
   </x:si>
   <x:si>
     <x:t>KOCMT</x:t>
   </x:si>
   <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
+    <x:t>KRPLS</x:t>
   </x:si>
   <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
+    <x:t>LILAK</x:t>
   </x:si>
   <x:si>
     <x:t>MTRYO</x:t>
@@ -224,25 +218,25 @@
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
+    <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
     <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -593,7 +587,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C34"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -945,28 +939,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1000,7 +972,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1011,7 +983,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1022,7 +994,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1033,7 +1005,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1044,7 +1016,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1055,7 +1027,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1066,7 +1038,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1077,7 +1049,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1088,7 +1060,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1099,7 +1071,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1110,7 +1082,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1121,7 +1093,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1132,7 +1104,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1143,7 +1115,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1154,7 +1126,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1165,7 +1137,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1176,7 +1148,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1187,7 +1159,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1198,7 +1170,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1209,7 +1181,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1220,7 +1192,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1231,7 +1203,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1242,7 +1214,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1253,7 +1225,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1264,7 +1236,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1275,7 +1247,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1286,7 +1258,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1297,7 +1269,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1308,7 +1280,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1319,7 +1291,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1330,7 +1302,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1341,7 +1313,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1352,7 +1324,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1363,7 +1335,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1374,7 +1346,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1385,7 +1357,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1396,7 +1368,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1407,7 +1379,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,196 +35,196 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARASE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
   </x:si>
   <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
-    <x:t>METRO</x:t>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
   </x:si>
   <x:si>
     <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
     <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
@@ -587,7 +587,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -939,6 +939,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -956,7 +989,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C39"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -972,7 +1005,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -983,7 +1016,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -994,7 +1027,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1005,7 +1038,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1016,7 +1049,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,7 +1060,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1038,7 +1071,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1049,7 +1082,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1060,7 +1093,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1071,7 +1104,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1082,7 +1115,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1093,7 +1126,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1104,7 +1137,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1115,7 +1148,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1126,7 +1159,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1137,7 +1170,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1148,7 +1181,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1159,7 +1192,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1170,7 +1203,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1181,7 +1214,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1192,7 +1225,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1203,7 +1236,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1214,7 +1247,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1225,7 +1258,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1236,7 +1269,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1247,7 +1280,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1258,7 +1291,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1269,7 +1302,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1280,7 +1313,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1291,7 +1324,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1302,7 +1335,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1313,7 +1346,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1324,7 +1357,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1335,7 +1368,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1346,45 +1379,12 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,217 +26,145 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
   </x:si>
   <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -587,7 +515,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -873,105 +801,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -989,7 +818,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1005,7 +834,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1016,7 +845,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,7 +856,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1038,7 +867,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1049,7 +878,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1060,7 +889,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1071,7 +900,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1082,7 +911,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1093,7 +922,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1104,7 +933,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1115,7 +944,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1126,7 +955,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1137,7 +966,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1148,7 +977,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1159,7 +988,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1170,7 +999,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1181,7 +1010,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1192,7 +1021,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1203,7 +1032,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1214,177 +1043,12 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,34 +26,31 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
-    <x:t>ASTOR</x:t>
+    <x:t>ASGYO</x:t>
   </x:si>
   <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>DAGI</x:t>
   </x:si>
   <x:si>
     <x:t>DMRGD</x:t>
@@ -68,97 +65,97 @@
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
     <x:t>ISGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
     <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
@@ -515,7 +512,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -768,39 +765,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -818,7 +782,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -834,7 +798,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -845,7 +809,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -856,7 +820,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -867,7 +831,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -878,7 +842,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -889,7 +853,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -900,7 +864,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -911,7 +875,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -922,7 +886,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -933,7 +897,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -944,7 +908,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -955,7 +919,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -966,7 +930,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -977,7 +941,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -988,7 +952,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -999,7 +963,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1010,7 +974,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1021,7 +985,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1032,7 +996,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1043,12 +1007,34 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -47,13 +47,100 @@
     <x:t>ASGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
   </x:si>
   <x:si>
     <x:t>DSTKF</x:t>
@@ -62,103 +149,67 @@
     <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
-    <x:t>ETILR</x:t>
+    <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
     <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TRALT</x:t>
@@ -512,7 +563,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -765,6 +816,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -782,7 +855,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -798,7 +871,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -809,7 +882,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -820,7 +893,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -831,7 +904,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -842,7 +915,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -853,7 +926,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -864,7 +937,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -875,7 +948,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -886,7 +959,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -897,7 +970,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -908,7 +981,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -919,7 +992,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -930,7 +1003,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -941,7 +1014,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -952,7 +1025,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -963,7 +1036,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -974,7 +1047,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -985,7 +1058,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -996,7 +1069,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1007,7 +1080,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1018,7 +1091,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1029,12 +1102,177 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,193 +26,166 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
     <x:t>KORDS</x:t>
   </x:si>
   <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
     <x:t>UFUK</x:t>
   </x:si>
   <x:si>
     <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -563,7 +536,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C25"/>
+  <x:dimension ref="A1:C19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -772,72 +745,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -855,7 +762,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C38"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -871,7 +778,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -882,7 +789,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -893,7 +800,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -904,7 +811,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -915,7 +822,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -926,7 +833,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -937,7 +844,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -948,7 +855,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -959,7 +866,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -970,7 +877,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -981,7 +888,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -992,7 +899,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1003,7 +910,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1014,7 +921,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1025,7 +932,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1036,7 +943,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1047,7 +954,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1058,7 +965,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1069,7 +976,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1080,7 +987,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1091,7 +998,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1102,7 +1009,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1113,7 +1020,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1124,7 +1031,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1135,7 +1042,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1146,7 +1053,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1157,7 +1064,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1168,7 +1075,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1179,7 +1086,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1190,7 +1097,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1201,7 +1108,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1212,7 +1119,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1223,7 +1130,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1234,45 +1141,12 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,120 +38,138 @@
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
   </x:si>
   <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>KORDS</x:t>
   </x:si>
   <x:si>
-    <x:t>KRONT</x:t>
+    <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MTRKS</x:t>
   </x:si>
   <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
     <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
@@ -173,19 +191,19 @@
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TRGYO</x:t>
+    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -762,7 +780,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1147,6 +1165,72 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,165 +26,195 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
     <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
   </x:si>
   <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
     <x:t>ODAS</x:t>
   </x:si>
   <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
@@ -195,9 +225,6 @@
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -554,7 +581,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C19"/>
+  <x:dimension ref="A1:C28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -763,6 +790,105 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -796,7 +922,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -807,7 +933,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -818,7 +944,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -829,7 +955,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -840,7 +966,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -851,7 +977,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -862,7 +988,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -873,7 +999,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -884,7 +1010,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -895,7 +1021,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -906,7 +1032,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -917,7 +1043,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -928,7 +1054,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -939,7 +1065,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -950,7 +1076,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -961,7 +1087,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -972,7 +1098,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -983,7 +1109,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -994,7 +1120,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1005,7 +1131,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1016,7 +1142,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,7 +1153,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1038,7 +1164,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1049,7 +1175,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1060,7 +1186,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1071,7 +1197,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1082,7 +1208,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1093,7 +1219,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1104,7 +1230,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1115,7 +1241,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1126,7 +1252,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1137,7 +1263,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1148,7 +1274,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1159,7 +1285,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1170,7 +1296,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1181,7 +1307,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1192,7 +1318,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1203,7 +1329,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1214,7 +1340,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1225,7 +1351,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,150 +26,168 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
     <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSOKE</x:t>
   </x:si>
   <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
     <x:t>CCOLA</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
   </x:si>
   <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
     <x:t>GESAN</x:t>
   </x:si>
   <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
@@ -179,13 +197,19 @@
     <x:t>ISGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
-    <x:t>KTLEV</x:t>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>MERCN</x:t>
@@ -200,28 +224,22 @@
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
     <x:t>POLHO</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
@@ -581,7 +599,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C28"/>
+  <x:dimension ref="A1:C25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -856,39 +874,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -906,7 +891,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C41"/>
+  <x:dimension ref="A1:C50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -922,7 +907,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -933,7 +918,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -944,7 +929,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -955,7 +940,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -966,7 +951,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -977,7 +962,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -988,7 +973,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -999,7 +984,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1010,7 +995,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1021,7 +1006,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1032,7 +1017,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1043,7 +1028,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1054,7 +1039,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1065,7 +1050,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1076,7 +1061,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1087,7 +1072,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1098,7 +1083,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1109,7 +1094,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1120,7 +1105,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1131,7 +1116,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1142,7 +1127,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1153,7 +1138,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1164,7 +1149,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1175,7 +1160,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1186,7 +1171,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1197,7 +1182,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1208,7 +1193,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1219,7 +1204,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1230,7 +1215,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1241,7 +1226,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1252,7 +1237,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1263,7 +1248,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1274,7 +1259,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1285,7 +1270,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1296,7 +1281,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1307,7 +1292,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1318,7 +1303,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1329,7 +1314,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1340,7 +1325,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1351,12 +1336,111 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -41,6 +41,9 @@
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
@@ -56,6 +59,12 @@
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
@@ -65,9 +74,15 @@
     <x:t>EGEPO</x:t>
   </x:si>
   <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>HATSN</x:t>
   </x:si>
   <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>IZMDC</x:t>
   </x:si>
   <x:si>
@@ -77,9 +92,15 @@
     <x:t>KRDMA</x:t>
   </x:si>
   <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
@@ -89,166 +110,145 @@
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>OZYSR</x:t>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>SOKE</x:t>
   </x:si>
   <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -599,7 +599,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C25"/>
+  <x:dimension ref="A1:C31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -874,6 +874,72 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -891,7 +957,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C50"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -907,7 +973,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -918,7 +984,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -929,7 +995,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -940,7 +1006,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -951,7 +1017,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -962,7 +1028,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -973,7 +1039,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -984,7 +1050,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -995,7 +1061,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1006,7 +1072,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1017,7 +1083,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1028,7 +1094,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1039,7 +1105,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1050,7 +1116,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1061,7 +1127,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1072,7 +1138,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1083,7 +1149,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1094,7 +1160,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1105,7 +1171,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1116,7 +1182,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1127,7 +1193,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1138,7 +1204,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1149,7 +1215,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1160,7 +1226,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1171,7 +1237,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1182,7 +1248,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1193,7 +1259,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1204,7 +1270,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1215,7 +1281,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1226,7 +1292,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1237,7 +1303,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1248,7 +1314,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1259,7 +1325,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1270,7 +1336,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1281,7 +1347,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1292,7 +1358,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1303,7 +1369,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1314,7 +1380,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1325,7 +1391,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1336,7 +1402,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1347,7 +1413,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1358,7 +1424,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1369,78 +1435,12 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,70 +26,175 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALARK</x:t>
   </x:si>
   <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>EGEGY</x:t>
   </x:si>
   <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMD</x:t>
@@ -101,151 +206,40 @@
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
@@ -599,7 +593,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C31"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -940,6 +934,61 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -957,7 +1006,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -973,7 +1022,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -984,7 +1033,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -995,7 +1044,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1006,7 +1055,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1017,7 +1066,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1028,7 +1077,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1039,7 +1088,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1050,7 +1099,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1061,7 +1110,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1072,7 +1121,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1083,7 +1132,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1094,7 +1143,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1105,7 +1154,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1116,7 +1165,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1127,7 +1176,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1138,7 +1187,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1149,7 +1198,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1160,7 +1209,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1171,7 +1220,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1182,7 +1231,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1193,7 +1242,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1204,7 +1253,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1215,7 +1264,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1226,7 +1275,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1237,7 +1286,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1248,7 +1297,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1259,7 +1308,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1270,7 +1319,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1281,7 +1330,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1292,7 +1341,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1303,7 +1352,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1314,7 +1363,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1325,7 +1374,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1336,7 +1385,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1347,7 +1396,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1358,89 +1407,12 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -47,202 +47,211 @@
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BIGEN</x:t>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
     <x:t>KARTN</x:t>
   </x:si>
   <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -593,7 +602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -967,28 +976,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1006,7 +993,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C37"/>
+  <x:dimension ref="A1:C42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1022,7 +1009,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1033,7 +1020,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1044,7 +1031,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1055,7 +1042,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1066,7 +1053,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1077,7 +1064,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1088,7 +1075,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1099,7 +1086,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1110,7 +1097,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1121,7 +1108,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1132,7 +1119,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1143,7 +1130,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1154,7 +1141,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1165,7 +1152,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1176,7 +1163,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1187,7 +1174,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1198,7 +1185,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1209,7 +1196,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1220,7 +1207,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1231,7 +1218,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1242,7 +1229,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1253,7 +1240,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1264,7 +1251,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1275,7 +1262,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1286,7 +1273,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1297,7 +1284,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1308,7 +1295,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1319,7 +1306,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1330,7 +1317,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1341,7 +1328,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1352,7 +1339,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1363,7 +1350,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1374,7 +1361,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1385,7 +1372,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1396,7 +1383,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1407,12 +1394,67 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,19 +35,130 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>ARMGD</x:t>
@@ -56,202 +167,79 @@
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
     <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
+    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -602,7 +590,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C34"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -976,6 +964,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -993,7 +1003,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C42"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1009,7 +1019,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1020,7 +1030,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1031,7 +1041,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1042,7 +1052,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1053,7 +1063,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1064,7 +1074,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1075,7 +1085,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1086,7 +1096,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1097,7 +1107,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1108,7 +1118,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1129,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1140,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1151,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1162,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1173,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1184,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1195,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1206,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1217,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1228,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1239,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1250,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1261,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1272,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1283,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1294,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1305,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1306,7 +1316,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1317,7 +1327,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1328,7 +1338,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1339,7 +1349,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1350,7 +1360,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1361,7 +1371,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1372,7 +1382,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1383,78 +1393,12 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AEFES</x:t>
+    <x:t>ANELE</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,205 +35,136 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
+    <x:t>ATATP</x:t>
   </x:si>
   <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CCOLA</x:t>
   </x:si>
   <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
+    <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
     <x:t>EDATA</x:t>
   </x:si>
   <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
+    <x:t>EGEGY</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
     <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
@@ -590,7 +521,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -810,182 +741,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1003,7 +758,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1019,7 +774,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1030,7 +785,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1041,7 +796,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1052,7 +807,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1063,7 +818,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1074,7 +829,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1085,7 +840,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1096,7 +851,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1107,7 +862,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1118,7 +873,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1129,7 +884,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1140,7 +895,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1151,7 +906,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1162,7 +917,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1173,7 +928,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1184,7 +939,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1195,7 +950,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1206,7 +961,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1217,7 +972,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1228,7 +983,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1239,7 +994,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1250,7 +1005,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1261,7 +1016,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1272,7 +1027,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1283,7 +1038,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1294,7 +1049,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1305,7 +1060,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1316,89 +1071,12 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
+    <x:t>AKSA</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,28 +35,88 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
     <x:t>EREGL</x:t>
   </x:si>
   <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
     <x:t>IEYHO</x:t>
@@ -65,94 +125,13 @@
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
     <x:t>KOCMT</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
@@ -161,16 +140,22 @@
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -521,7 +506,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C20"/>
+  <x:dimension ref="A1:C19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -730,17 +715,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -758,7 +732,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C29"/>
+  <x:dimension ref="A1:C25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -774,7 +748,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -785,7 +759,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -796,7 +770,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -807,7 +781,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -818,7 +792,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -829,7 +803,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -840,7 +814,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -851,7 +825,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -862,7 +836,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -873,7 +847,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -884,7 +858,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -895,7 +869,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -906,7 +880,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -917,7 +891,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -928,7 +902,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -939,7 +913,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -950,7 +924,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -961,7 +935,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -972,7 +946,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -983,7 +957,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -994,7 +968,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1005,7 +979,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1016,7 +990,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,56 +1001,12 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,136 +26,130 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
   </x:si>
   <x:si>
     <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -506,7 +500,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C19"/>
+  <x:dimension ref="A1:C22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -715,6 +709,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -732,7 +759,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C25"/>
+  <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -748,7 +775,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -759,7 +786,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -770,7 +797,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -781,7 +808,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -792,7 +819,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -803,7 +830,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -814,7 +841,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -825,7 +852,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -836,7 +863,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -847,7 +874,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -858,7 +885,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -869,7 +896,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -880,7 +907,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -891,7 +918,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -902,7 +929,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -913,7 +940,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -924,7 +951,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -935,7 +962,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -946,67 +973,12 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,121 +35,88 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
     <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>PAGYO</x:t>
+    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -500,7 +467,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C22"/>
+  <x:dimension ref="A1:C17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -687,61 +654,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -759,7 +671,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C20"/>
+  <x:dimension ref="A1:C14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -775,7 +687,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -786,7 +698,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -797,7 +709,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -808,7 +720,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -819,7 +731,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -830,7 +742,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -841,7 +753,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -852,7 +764,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -863,7 +775,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -874,7 +786,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -885,7 +797,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -896,7 +808,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -907,78 +819,12 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,13 +35,16 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>CCOLA</x:t>
+    <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
     <x:t>GEREL</x:t>
@@ -50,73 +53,61 @@
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KMPUR</x:t>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
   </x:si>
   <x:si>
     <x:t>KOCMT</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>OZATD</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -467,7 +458,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C17"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -632,28 +623,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -671,7 +640,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C14"/>
+  <x:dimension ref="A1:C13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -687,7 +656,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -698,7 +667,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -709,7 +678,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -720,7 +689,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -731,7 +700,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -742,7 +711,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -753,7 +722,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -764,7 +733,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -775,7 +744,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -786,7 +755,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -797,7 +766,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -808,23 +777,12 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,79 +35,133 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
   </x:si>
   <x:si>
     <x:t>GEREL</x:t>
   </x:si>
   <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
     <x:t>KUVVA</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
+    <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -458,7 +512,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -623,6 +677,61 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -640,7 +749,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C13"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -656,7 +765,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -667,7 +776,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -678,7 +787,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -689,7 +798,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -700,7 +809,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -711,7 +820,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -722,7 +831,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -733,7 +842,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -744,7 +853,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -755,7 +864,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -766,7 +875,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -777,12 +886,155 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,10 +35,7 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
+    <x:t>ANHYT</x:t>
   </x:si>
   <x:si>
     <x:t>ARDYZ</x:t>
@@ -47,121 +44,118 @@
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>CRFSA</x:t>
+    <x:t>CELHA</x:t>
   </x:si>
   <x:si>
     <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -512,7 +506,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C20"/>
+  <x:dimension ref="A1:C24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -732,6 +726,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -749,7 +787,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -765,7 +803,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -776,7 +814,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -787,7 +825,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -798,7 +836,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -809,7 +847,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -820,7 +858,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -831,7 +869,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -842,7 +880,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -853,7 +891,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -864,7 +902,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -875,7 +913,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -886,7 +924,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -897,7 +935,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -908,7 +946,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -919,7 +957,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -930,7 +968,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -941,7 +979,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -952,7 +990,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -963,78 +1001,12 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AEFES</x:t>
+    <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -41,46 +41,142 @@
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
   </x:si>
   <x:si>
     <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
   </x:si>
   <x:si>
     <x:t>RYSAS</x:t>
@@ -89,73 +185,19 @@
     <x:t>SEKUR</x:t>
   </x:si>
   <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>UFUK</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
+    <x:t>VBTYZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -506,7 +548,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C24"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -759,17 +801,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -787,7 +818,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C20"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -803,7 +834,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -814,7 +845,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -825,7 +856,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -836,7 +867,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -847,7 +878,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -858,7 +889,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -869,7 +900,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -880,7 +911,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -891,7 +922,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -902,7 +933,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -913,7 +944,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -924,7 +955,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -935,7 +966,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -946,7 +977,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -957,7 +988,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -968,7 +999,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -979,7 +1010,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -990,7 +1021,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1001,12 +1032,177 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,178 +26,199 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
+    <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
   </x:si>
   <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>MARKA</x:t>
   </x:si>
   <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
+    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TGSAS</x:t>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -548,7 +569,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -801,6 +822,116 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -818,7 +949,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -834,7 +965,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -845,7 +976,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -856,7 +987,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -867,7 +998,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -878,7 +1009,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -889,7 +1020,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -900,7 +1031,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -911,7 +1042,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -922,7 +1053,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -933,7 +1064,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -944,7 +1075,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -955,7 +1086,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -966,7 +1097,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -977,7 +1108,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -988,7 +1119,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -999,7 +1130,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1010,7 +1141,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1021,7 +1152,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1032,7 +1163,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1043,7 +1174,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1054,7 +1185,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1065,7 +1196,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1076,7 +1207,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1087,7 +1218,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1098,7 +1229,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1109,7 +1240,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1120,7 +1251,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1131,7 +1262,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1142,7 +1273,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1153,7 +1284,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1164,45 +1295,12 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AGHOL</x:t>
+    <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,43 +35,136 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>IEYHO</x:t>
@@ -80,139 +173,46 @@
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
   </x:si>
   <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
+    <x:t>MARKA</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
@@ -569,7 +569,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -921,17 +921,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -949,7 +938,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -965,7 +954,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -976,7 +965,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -987,7 +976,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -998,7 +987,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1009,7 +998,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1020,7 +1009,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1031,7 +1020,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1042,7 +1031,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1053,7 +1042,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1064,7 +1053,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1075,7 +1064,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1086,7 +1075,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1097,7 +1086,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1108,7 +1097,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1108,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1119,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1130,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1141,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1152,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1163,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1174,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1185,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1196,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1207,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1218,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1229,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1240,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1251,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1262,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1273,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,12 +1284,23 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -44,15 +44,9 @@
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
     <x:t>DOCO</x:t>
   </x:si>
   <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
     <x:t>EDATA</x:t>
   </x:si>
   <x:si>
@@ -62,154 +56,160 @@
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEREL</x:t>
   </x:si>
   <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
   </x:si>
   <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TNZTP</x:t>
@@ -569,7 +569,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -899,28 +899,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -938,7 +916,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -954,7 +932,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -965,7 +943,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -976,7 +954,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -987,7 +965,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -998,7 +976,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1009,7 +987,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1020,7 +998,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1031,7 +1009,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1042,7 +1020,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1053,7 +1031,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1064,7 +1042,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1075,7 +1053,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1086,7 +1064,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1097,7 +1075,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1108,7 +1086,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1097,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1108,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1119,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1130,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1141,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1152,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1163,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1174,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1185,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1196,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1207,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1218,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1229,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1240,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1251,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1262,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,12 +1273,34 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,55 +26,175 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>ANSGR</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
   </x:si>
   <x:si>
     <x:t>ODINE</x:t>
@@ -83,142 +203,34 @@
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>TRENJ</x:t>
   </x:si>
   <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>UFUK</x:t>
+    <x:t>VERUS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -569,7 +581,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C30"/>
+  <x:dimension ref="A1:C34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -899,6 +911,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -932,7 +988,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -943,7 +999,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -954,7 +1010,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -965,7 +1021,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -976,7 +1032,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -987,7 +1043,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -998,7 +1054,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1009,7 +1065,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1020,7 +1076,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1031,7 +1087,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1042,7 +1098,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1053,7 +1109,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1064,7 +1120,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1075,7 +1131,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1086,7 +1142,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1097,7 +1153,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1108,7 +1164,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1175,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1186,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1197,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1208,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1219,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1230,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1241,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1252,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1263,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1274,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1285,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1296,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1307,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1318,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1329,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1340,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1351,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
+    <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,28 +35,34 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>ANSGR</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
     <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CVKMD</x:t>
+    <x:t>CWENE</x:t>
   </x:si>
   <x:si>
     <x:t>DAGI</x:t>
@@ -65,6 +71,15 @@
     <x:t>DOAS</x:t>
   </x:si>
   <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
@@ -74,163 +89,127 @@
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>GOZDE</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
   </x:si>
   <x:si>
     <x:t>KCAER</x:t>
   </x:si>
   <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TMPOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -581,7 +560,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C34"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -955,6 +934,61 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -972,7 +1006,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -988,7 +1022,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -999,7 +1033,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1010,7 +1044,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1021,7 +1055,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1032,7 +1066,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1043,7 +1077,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1054,7 +1088,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1065,7 +1099,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1076,7 +1110,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1087,7 +1121,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1098,7 +1132,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1109,7 +1143,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1120,7 +1154,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1131,7 +1165,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1142,7 +1176,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1153,7 +1187,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1164,7 +1198,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1175,7 +1209,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1186,7 +1220,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1197,7 +1231,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1208,7 +1242,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1219,144 +1253,12 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,24 +35,24 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
     <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
@@ -62,16 +62,19 @@
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>CUSAN</x:t>
   </x:si>
   <x:si>
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
     <x:t>DOAS</x:t>
   </x:si>
   <x:si>
-    <x:t>DUNYH</x:t>
+    <x:t>DOCO</x:t>
   </x:si>
   <x:si>
     <x:t>EDIP</x:t>
@@ -83,133 +86,154 @@
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
   </x:si>
   <x:si>
     <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
   </x:si>
   <x:si>
     <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -560,7 +584,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C39"/>
+  <x:dimension ref="A1:C41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -989,6 +1013,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1006,7 +1052,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1022,7 +1068,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1033,7 +1079,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1044,7 +1090,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1055,7 +1101,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1066,7 +1112,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1077,7 +1123,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1088,7 +1134,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1099,7 +1145,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1110,7 +1156,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1121,7 +1167,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1132,7 +1178,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1143,7 +1189,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1154,7 +1200,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1165,7 +1211,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1176,7 +1222,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1187,7 +1233,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1198,7 +1244,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1209,7 +1255,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1220,7 +1266,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1231,7 +1277,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1242,7 +1288,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1253,12 +1299,78 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,214 +26,226 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
     <x:t>ANSGR</x:t>
   </x:si>
   <x:si>
-    <x:t>ASTOR</x:t>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
+    <x:t>DEVA</x:t>
   </x:si>
   <x:si>
     <x:t>DGNMO</x:t>
   </x:si>
   <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
   </x:si>
   <x:si>
     <x:t>GESAN</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
     <x:t>ISGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
   </x:si>
   <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -584,7 +596,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C41"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -980,61 +992,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1052,7 +1009,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C29"/>
+  <x:dimension ref="A1:C38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1068,7 +1025,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1079,7 +1036,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1090,7 +1047,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1101,7 +1058,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1112,7 +1069,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1123,7 +1080,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1134,7 +1091,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1145,7 +1102,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1156,7 +1113,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1167,7 +1124,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1178,7 +1135,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1189,7 +1146,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1200,7 +1157,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1211,7 +1168,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1222,7 +1179,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1233,7 +1190,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1244,7 +1201,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1255,7 +1212,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1266,7 +1223,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1277,7 +1234,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1288,7 +1245,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1299,7 +1256,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1310,7 +1267,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1321,7 +1278,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1332,7 +1289,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1343,7 +1300,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1354,7 +1311,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1365,12 +1322,111 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,49 +26,178 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
   </x:si>
   <x:si>
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
@@ -77,175 +206,52 @@
     <x:t>HURGZ</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
   </x:si>
   <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
   </x:si>
   <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
-    <x:t>PRDGS</x:t>
+    <x:t>RALYH</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
+    <x:t>VBTYZ</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -596,7 +602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -992,6 +998,83 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1009,7 +1092,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C38"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1025,7 +1108,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1036,7 +1119,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1047,7 +1130,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1058,7 +1141,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1069,7 +1152,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1080,7 +1163,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1091,7 +1174,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1102,7 +1185,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1113,7 +1196,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1124,7 +1207,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1135,7 +1218,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1146,7 +1229,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1157,7 +1240,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1168,7 +1251,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1179,7 +1262,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1190,7 +1273,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1201,7 +1284,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1212,7 +1295,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1223,7 +1306,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1234,7 +1317,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1245,7 +1328,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1256,7 +1339,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1267,7 +1350,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1278,7 +1361,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1289,7 +1372,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1300,7 +1383,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1311,7 +1394,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1322,7 +1405,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1333,7 +1416,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1344,7 +1427,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1355,7 +1438,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1366,67 +1449,12 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,6 +38,12 @@
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
@@ -47,24 +53,30 @@
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
@@ -83,175 +95,166 @@
     <x:t>ENDAE</x:t>
   </x:si>
   <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ESCOM</x:t>
   </x:si>
   <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>ISFIN</x:t>
   </x:si>
   <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
     <x:t>PASEU</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
   </x:si>
   <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
+    <x:t>ULUSE</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -602,7 +605,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C43"/>
+  <x:dimension ref="A1:C48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1075,6 +1078,61 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1092,7 +1150,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1108,7 +1166,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1177,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1188,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1199,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1210,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1221,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1232,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1243,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1254,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1265,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1276,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1287,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1298,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1309,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1320,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1331,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1342,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1353,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1306,7 +1364,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1317,7 +1375,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1328,7 +1386,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1339,7 +1397,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1350,7 +1408,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1361,7 +1419,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1372,7 +1430,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1383,7 +1441,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1394,7 +1452,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1405,56 +1463,12 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,100 +26,184 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSUE</x:t>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
   </x:si>
   <x:si>
     <x:t>METRO</x:t>
@@ -128,133 +212,28 @@
     <x:t>MTRKS</x:t>
   </x:si>
   <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
+    <x:t>TUPRS</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -605,7 +584,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C48"/>
+  <x:dimension ref="A1:C43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1078,61 +1057,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1150,7 +1074,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C29"/>
+  <x:dimension ref="A1:C27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1166,7 +1090,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1177,7 +1101,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1188,7 +1112,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1199,7 +1123,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1210,7 +1134,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1221,7 +1145,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1232,7 +1156,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1243,7 +1167,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1254,7 +1178,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1265,7 +1189,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1276,7 +1200,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1287,7 +1211,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1298,7 +1222,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1309,7 +1233,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1320,7 +1244,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1331,7 +1255,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1342,7 +1266,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1353,7 +1277,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1364,7 +1288,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1375,7 +1299,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1386,7 +1310,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1397,7 +1321,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1408,7 +1332,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1419,7 +1343,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1430,7 +1354,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1441,34 +1365,12 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,202 +35,250 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
   </x:si>
   <x:si>
     <x:t>ENDAE</x:t>
   </x:si>
   <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
     <x:t>POLHO</x:t>
   </x:si>
   <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
+    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
@@ -584,7 +632,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C43"/>
+  <x:dimension ref="A1:C51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1057,6 +1105,94 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1074,7 +1210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C27"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1090,7 +1226,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1101,7 +1237,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1112,7 +1248,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1123,7 +1259,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1134,7 +1270,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1145,7 +1281,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1156,7 +1292,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1167,7 +1303,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1178,7 +1314,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1189,7 +1325,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1200,7 +1336,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1211,7 +1347,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1222,7 +1358,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1233,7 +1369,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1244,7 +1380,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1255,7 +1391,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1266,7 +1402,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1277,7 +1413,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1288,7 +1424,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1299,7 +1435,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1310,7 +1446,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1321,7 +1457,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1332,7 +1468,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1343,7 +1479,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1354,7 +1490,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1365,12 +1501,100 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -44,238 +44,244 @@
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>ASELS</x:t>
   </x:si>
   <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
+    <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
   </x:si>
   <x:si>
     <x:t>EDATA</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>HUNER</x:t>
   </x:si>
   <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
   </x:si>
   <x:si>
     <x:t>PRDGS</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>TRALT</x:t>
@@ -632,7 +638,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C51"/>
+  <x:dimension ref="A1:C52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1193,6 +1199,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1210,7 +1227,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1226,7 +1243,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1237,7 +1254,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1248,7 +1265,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1259,7 +1276,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1270,7 +1287,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1281,7 +1298,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1292,7 +1309,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1303,7 +1320,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1314,7 +1331,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1325,7 +1342,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1336,7 +1353,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1347,7 +1364,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1358,7 +1375,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1369,7 +1386,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1380,7 +1397,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1391,7 +1408,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1402,7 +1419,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1413,7 +1430,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1424,7 +1441,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1435,7 +1452,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1446,7 +1463,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1457,7 +1474,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1468,7 +1485,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1479,7 +1496,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1490,7 +1507,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1501,7 +1518,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1512,7 +1529,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1523,7 +1540,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1534,7 +1551,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1545,7 +1562,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1556,7 +1573,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1567,7 +1584,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1578,7 +1595,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1589,12 +1606,23 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,25 +38,172 @@
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARASE</x:t>
   </x:si>
   <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATATP</x:t>
   </x:si>
   <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BAHKM</x:t>
+    <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
     <x:t>BIMAS</x:t>
@@ -65,52 +212,43 @@
     <x:t>BINBN</x:t>
   </x:si>
   <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
   </x:si>
   <x:si>
     <x:t>GESAN</x:t>
   </x:si>
   <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
   </x:si>
   <x:si>
     <x:t>KUVVA</x:t>
@@ -119,13 +257,7 @@
     <x:t>MARKA</x:t>
   </x:si>
   <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
+    <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
     <x:t>OZSUB</x:t>
@@ -134,160 +266,40 @@
     <x:t>PASEU</x:t>
   </x:si>
   <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
   </x:si>
   <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -638,7 +650,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C52"/>
+  <x:dimension ref="A1:C49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1177,39 +1189,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1227,7 +1206,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1243,7 +1222,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1254,7 +1233,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1265,7 +1244,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1276,7 +1255,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1287,7 +1266,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1298,7 +1277,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1309,7 +1288,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1320,7 +1299,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1331,7 +1310,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1342,7 +1321,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1353,7 +1332,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1364,7 +1343,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1375,7 +1354,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1386,7 +1365,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1397,7 +1376,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1408,7 +1387,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1419,7 +1398,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1430,7 +1409,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1441,7 +1420,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1452,7 +1431,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1463,7 +1442,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1474,7 +1453,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1485,7 +1464,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1496,7 +1475,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1507,7 +1486,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1518,7 +1497,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1529,7 +1508,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1540,7 +1519,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1551,7 +1530,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1562,7 +1541,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1573,7 +1552,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1584,7 +1563,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1595,7 +1574,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1606,7 +1585,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1617,12 +1596,89 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,7 +38,7 @@
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
-    <x:t>ALKLC</x:t>
+    <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
     <x:t>ASTOR</x:t>
@@ -47,6 +47,9 @@
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
@@ -56,241 +59,217 @@
     <x:t>CEMZY</x:t>
   </x:si>
   <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
     <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
-    <x:t>ENDAE</x:t>
+    <x:t>DURKN</x:t>
   </x:si>
   <x:si>
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
   </x:si>
   <x:si>
     <x:t>KCAER</x:t>
   </x:si>
   <x:si>
-    <x:t>KCHOL</x:t>
+    <x:t>KERVN</x:t>
   </x:si>
   <x:si>
     <x:t>KGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>KRPLS</x:t>
   </x:si>
   <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>SANFM</x:t>
   </x:si>
   <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEGMN</x:t>
   </x:si>
   <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
@@ -650,7 +629,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C49"/>
+  <x:dimension ref="A1:C46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1156,39 +1135,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1206,7 +1152,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C43"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1222,7 +1168,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1233,7 +1179,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1244,7 +1190,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1255,7 +1201,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1266,7 +1212,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1277,7 +1223,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1288,7 +1234,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1299,7 +1245,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1310,7 +1256,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1321,7 +1267,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1332,7 +1278,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1343,7 +1289,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1354,7 +1300,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1365,7 +1311,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1376,7 +1322,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1387,7 +1333,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1398,7 +1344,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1409,7 +1355,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1420,7 +1366,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1431,7 +1377,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1442,7 +1388,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1453,7 +1399,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1464,7 +1410,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1475,7 +1421,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1486,7 +1432,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1497,7 +1443,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1508,7 +1454,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1519,7 +1465,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1530,7 +1476,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1541,7 +1487,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1552,7 +1498,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1563,7 +1509,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1574,7 +1520,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1585,7 +1531,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1596,7 +1542,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1607,7 +1553,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1618,7 +1564,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1629,56 +1575,12 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -41,244 +41,217 @@
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -629,7 +602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C46"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1113,28 +1086,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1152,7 +1103,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C39"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1168,7 +1119,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1179,7 +1130,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1190,7 +1141,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1201,7 +1152,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1212,7 +1163,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1223,7 +1174,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1234,7 +1185,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1245,7 +1196,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1256,7 +1207,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1267,7 +1218,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1278,7 +1229,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1289,7 +1240,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1300,7 +1251,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1311,7 +1262,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1322,7 +1273,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1333,7 +1284,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1344,7 +1295,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1355,7 +1306,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1366,7 +1317,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1377,7 +1328,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1388,7 +1339,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1399,7 +1350,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1410,7 +1361,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1421,7 +1372,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1432,7 +1383,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1443,7 +1394,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1454,7 +1405,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1465,7 +1416,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1476,7 +1427,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1487,7 +1438,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1498,89 +1449,12 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,22 +26,34 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
-    <x:t>ARDYZ</x:t>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
     <x:t>BAHKM</x:t>
@@ -50,7 +62,7 @@
     <x:t>BIGTK</x:t>
   </x:si>
   <x:si>
-    <x:t>BRSAN</x:t>
+    <x:t>BRLSM</x:t>
   </x:si>
   <x:si>
     <x:t>CEMZY</x:t>
@@ -62,13 +74,16 @@
     <x:t>DURKN</x:t>
   </x:si>
   <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
     <x:t>EGEGY</x:t>
   </x:si>
   <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
@@ -83,172 +98,157 @@
     <x:t>HATSN</x:t>
   </x:si>
   <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
   </x:si>
   <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
+    <x:t>MTRKS</x:t>
   </x:si>
   <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>PCILT</x:t>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
   </x:si>
   <x:si>
     <x:t>PSDTC</x:t>
   </x:si>
   <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
   </x:si>
   <x:si>
     <x:t>TRENJ</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
@@ -602,7 +602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1020,72 +1020,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1103,7 +1037,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1119,7 +1053,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1064,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1075,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1086,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1097,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1108,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1119,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1130,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1141,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1152,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1163,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1174,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1185,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1196,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1207,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1218,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1229,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1306,7 +1240,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1317,7 +1251,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1328,7 +1262,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1339,7 +1273,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1350,7 +1284,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1361,7 +1295,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1372,7 +1306,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1383,7 +1317,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1394,7 +1328,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1405,7 +1339,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1416,7 +1350,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1427,7 +1361,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1438,7 +1372,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1449,12 +1383,78 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,10 +38,106 @@
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
     <x:t>ALARK</x:t>
@@ -50,202 +146,118 @@
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
   </x:si>
   <x:si>
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>EGEGY</x:t>
   </x:si>
   <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
+    <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
   </x:si>
   <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMA</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
   </x:si>
   <x:si>
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>PKART</x:t>
   </x:si>
   <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
     <x:t>PSDTC</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRALT</x:t>
   </x:si>
   <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
@@ -602,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C38"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -998,28 +1010,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1037,7 +1027,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C38"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1053,7 +1043,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1064,7 +1054,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1075,7 +1065,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1086,7 +1076,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1097,7 +1087,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1108,7 +1098,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1119,7 +1109,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1130,7 +1120,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1141,7 +1131,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1152,7 +1142,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1163,7 +1153,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1174,7 +1164,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1185,7 +1175,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1196,7 +1186,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1207,7 +1197,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1218,7 +1208,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1229,7 +1219,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1240,7 +1230,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1251,7 +1241,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1262,7 +1252,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1273,7 +1263,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1284,7 +1274,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1295,7 +1285,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1306,7 +1296,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1317,7 +1307,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1328,7 +1318,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1339,7 +1329,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1350,7 +1340,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1361,7 +1351,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1372,7 +1362,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1383,7 +1373,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1394,7 +1384,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1405,7 +1395,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1416,7 +1406,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1427,7 +1417,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1438,7 +1428,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1449,12 +1439,78 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,46 +26,136 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
     <x:t>BRSAN</x:t>
@@ -74,196 +164,112 @@
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TRMET</x:t>
   </x:si>
   <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
+    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -614,7 +620,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -977,39 +983,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1027,7 +1000,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1043,7 +1016,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1054,7 +1027,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1065,7 +1038,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1076,7 +1049,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1087,7 +1060,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1098,7 +1071,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1109,7 +1082,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1120,7 +1093,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1131,7 +1104,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1142,7 +1115,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1153,7 +1126,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1164,7 +1137,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1175,7 +1148,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1186,7 +1159,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1197,7 +1170,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1208,7 +1181,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1219,7 +1192,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1230,7 +1203,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1241,7 +1214,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1252,7 +1225,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1263,7 +1236,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1274,7 +1247,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -1285,7 +1258,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -1296,7 +1269,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -1307,7 +1280,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -1318,7 +1291,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -1329,7 +1302,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -1340,7 +1313,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -1351,7 +1324,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -1362,7 +1335,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -1373,7 +1346,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -1384,7 +1357,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1395,7 +1368,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1406,7 +1379,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1417,7 +1390,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -1428,7 +1401,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -1439,7 +1412,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -1450,7 +1423,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -1461,7 +1434,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -1472,7 +1445,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -1483,7 +1456,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -1494,7 +1467,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -1505,12 +1478,67 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,18 +26,18 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
@@ -47,229 +47,124 @@
     <x:t>ARSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>ASTOR</x:t>
+    <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
-    <x:t>BIGTK</x:t>
+    <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
     <x:t>BRLSM</x:t>
   </x:si>
   <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>CVKMD</x:t>
   </x:si>
   <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>DOHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>RALYH</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -620,7 +515,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C33"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -972,17 +867,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1000,7 +884,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C49"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1016,7 +900,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -1027,7 +911,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -1038,7 +922,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -1049,7 +933,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -1060,7 +944,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -1071,7 +955,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -1082,7 +966,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -1093,7 +977,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -1104,7 +988,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -1115,7 +999,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1126,7 +1010,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1137,7 +1021,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -1148,7 +1032,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -1159,386 +1043,12 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -44,9 +44,6 @@
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
@@ -56,51 +53,24 @@
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
-    <x:t>BRLSM</x:t>
+    <x:t>CATES</x:t>
   </x:si>
   <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
     <x:t>HUNER</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMA</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
+    <x:t>MANAS</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
@@ -122,49 +92,40 @@
     <x:t>TUPRS</x:t>
   </x:si>
   <x:si>
-    <x:t>YGGYO</x:t>
+    <x:t>ARASE</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUVVA</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
   </x:si>
   <x:si>
     <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -515,7 +476,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -746,127 +707,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -884,7 +724,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -900,7 +740,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -911,7 +751,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -922,7 +762,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -933,7 +773,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -944,7 +784,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -955,7 +795,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -966,7 +806,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -977,7 +817,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -988,7 +828,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -999,7 +839,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -1010,7 +850,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -1021,34 +861,12 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,106 +26,88 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>ALARK</x:t>
   </x:si>
   <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
+    <x:t>POLHO</x:t>
   </x:si>
   <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
+    <x:t>VERUS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -476,7 +458,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -619,94 +601,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -724,7 +618,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C13"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -740,7 +634,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -751,7 +645,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -762,7 +656,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -773,7 +667,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -784,7 +678,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -795,7 +689,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -806,7 +700,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -817,7 +711,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -828,7 +722,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -839,7 +733,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -850,7 +744,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -861,12 +755,34 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,49 +35,64 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
+    <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>RYSAS</x:t>
+    <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>AGESA</x:t>
+    <x:t>TRCAS</x:t>
   </x:si>
   <x:si>
     <x:t>ALARK</x:t>
   </x:si>
   <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
@@ -86,28 +101,10 @@
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
     <x:t>SOKM</x:t>
   </x:si>
   <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -458,7 +455,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C13"/>
+  <x:dimension ref="A1:C19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -601,6 +598,72 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -618,7 +681,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -634,7 +697,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -645,7 +708,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -656,7 +719,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -667,7 +730,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -678,7 +741,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -689,7 +752,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -700,89 +763,12 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,19 +35,70 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
   </x:si>
   <x:si>
     <x:t>ENJSA</x:t>
@@ -56,55 +107,40 @@
     <x:t>ETYAT</x:t>
   </x:si>
   <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
   </x:si>
   <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
     <x:t>SOKM</x:t>
   </x:si>
   <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -455,7 +491,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C19"/>
+  <x:dimension ref="A1:C12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -587,83 +623,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -681,7 +640,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -697,7 +656,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -708,7 +667,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -719,7 +678,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -730,7 +689,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -741,7 +700,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -752,7 +711,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -763,12 +722,221 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,99 +35,96 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKCNS</x:t>
   </x:si>
   <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
     <x:t>NETAS</x:t>
   </x:si>
   <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
@@ -140,7 +137,7 @@
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>VBTYZ</x:t>
+    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -491,7 +488,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -623,6 +620,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -640,7 +659,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C27"/>
+  <x:dimension ref="A1:C24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -656,7 +675,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -667,7 +686,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -678,7 +697,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -689,7 +708,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -700,7 +719,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -711,7 +730,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -722,7 +741,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -733,7 +752,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -744,7 +763,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -755,7 +774,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -766,7 +785,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -777,7 +796,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -788,7 +807,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -799,7 +818,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -810,7 +829,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -821,7 +840,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -832,7 +851,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -843,7 +862,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -854,7 +873,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -865,7 +884,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -876,7 +895,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -887,7 +906,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -898,45 +917,12 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,109 +35,154 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARASE</x:t>
   </x:si>
   <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
   </x:si>
   <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>TRCAS</x:t>
   </x:si>
   <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
+    <x:t>TRENJ</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -488,7 +533,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C14"/>
+  <x:dimension ref="A1:C17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -642,6 +687,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -659,7 +737,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C24"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -675,7 +753,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -686,7 +764,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -697,7 +775,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -708,7 +786,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -719,7 +797,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -730,7 +808,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -741,7 +819,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -752,7 +830,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -763,7 +841,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -774,7 +852,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -785,7 +863,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -796,7 +874,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -807,7 +885,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -818,7 +896,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -829,7 +907,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -840,7 +918,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -851,7 +929,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -862,7 +940,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -873,7 +951,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -884,7 +962,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -895,7 +973,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -906,7 +984,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -917,12 +995,144 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,84 +35,90 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATSYH</x:t>
   </x:si>
   <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
     <x:t>AVPGY</x:t>
   </x:si>
   <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
@@ -122,57 +128,33 @@
     <x:t>EGPRO</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
     <x:t>GENIL</x:t>
   </x:si>
   <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
+    <x:t>NETAS</x:t>
   </x:si>
   <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
     <x:t>RALYH</x:t>
   </x:si>
   <x:si>
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRALT</x:t>
   </x:si>
   <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRENJ</x:t>
   </x:si>
   <x:si>
@@ -180,9 +162,6 @@
   </x:si>
   <x:si>
     <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -533,7 +512,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C17"/>
+  <x:dimension ref="A1:C25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -720,6 +699,94 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -737,7 +804,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -753,7 +820,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -764,7 +831,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -775,7 +842,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -786,7 +853,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -797,7 +864,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -808,7 +875,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -819,7 +886,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -830,7 +897,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -841,7 +908,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -852,7 +919,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -863,7 +930,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -874,7 +941,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -885,7 +952,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -896,7 +963,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -907,7 +974,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -918,7 +985,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -929,7 +996,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -940,7 +1007,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -951,7 +1018,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -962,177 +1029,12 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,142 +26,163 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>ENERY</x:t>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
   </x:si>
   <x:si>
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
     <x:t>SOKM</x:t>
   </x:si>
   <x:si>
-    <x:t>TARKM</x:t>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
   </x:si>
   <x:si>
     <x:t>TRCAS</x:t>
   </x:si>
   <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
     <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -512,7 +533,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C25"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -787,6 +808,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -804,7 +836,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -820,7 +852,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -831,7 +863,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -842,7 +874,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -853,7 +885,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -864,7 +896,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -875,7 +907,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -886,7 +918,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -897,7 +929,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -908,7 +940,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -919,7 +951,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -930,7 +962,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -941,7 +973,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -952,7 +984,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -963,7 +995,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -974,7 +1006,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -985,7 +1017,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -996,7 +1028,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1007,7 +1039,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1018,7 +1050,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1029,12 +1061,78 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
